--- a/data/듀링 법인차량 현황 ver.2.0.xlsx
+++ b/data/듀링 법인차량 현황 ver.2.0.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12444" windowHeight="10500" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12444" windowHeight="10500"/>
   </bookViews>
   <sheets>
     <sheet name="법인차량현황" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="235">
   <si>
     <t>차종</t>
   </si>
@@ -960,6 +960,37 @@
   </si>
   <si>
     <t>DR-CAR-02</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DR-CAR-13</t>
+  </si>
+  <si>
+    <t>205호1668</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>소나타 하이브리드</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>렌트</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이승민</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>기술연구소</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>우리금융캐피탈</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1544-8600</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1086,7 +1117,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -1284,6 +1315,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1296,7 +1338,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1600,19 +1642,16 @@
     <xf numFmtId="14" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="179" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1642,7 +1681,13 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2107,7 +2152,7 @@
         <f>ROW()-1</f>
         <v>1</v>
       </c>
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="102" t="s">
         <v>153</v>
       </c>
       <c r="C2" s="23" t="s">
@@ -2140,7 +2185,7 @@
       <c r="L2" s="25">
         <v>46836</v>
       </c>
-      <c r="M2" s="101">
+      <c r="M2" s="115">
         <v>1957670</v>
       </c>
       <c r="O2" s="15"/>
@@ -2150,7 +2195,7 @@
         <f t="shared" ref="A3:A17" si="0">ROW()-1</f>
         <v>2</v>
       </c>
-      <c r="B3" s="104" t="s">
+      <c r="B3" s="102" t="s">
         <v>154</v>
       </c>
       <c r="C3" s="18" t="s">
@@ -2183,7 +2228,7 @@
       <c r="L3" s="29">
         <v>46408</v>
       </c>
-      <c r="M3" s="102">
+      <c r="M3" s="30">
         <v>1921400</v>
       </c>
       <c r="O3" s="15"/>
@@ -2193,7 +2238,7 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B4" s="104" t="s">
+      <c r="B4" s="102" t="s">
         <v>155</v>
       </c>
       <c r="C4" s="18" t="s">
@@ -2226,7 +2271,7 @@
       <c r="L4" s="98">
         <v>46520</v>
       </c>
-      <c r="M4" s="102">
+      <c r="M4" s="30">
         <v>838100</v>
       </c>
       <c r="O4" s="15"/>
@@ -2236,7 +2281,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B5" s="104" t="s">
+      <c r="B5" s="102" t="s">
         <v>156</v>
       </c>
       <c r="C5" s="18" t="s">
@@ -2269,7 +2314,7 @@
       <c r="L5" s="98">
         <v>46474</v>
       </c>
-      <c r="M5" s="102">
+      <c r="M5" s="30">
         <v>928070</v>
       </c>
       <c r="O5" s="15"/>
@@ -2279,7 +2324,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B6" s="104" t="s">
+      <c r="B6" s="102" t="s">
         <v>157</v>
       </c>
       <c r="C6" s="18" t="s">
@@ -2312,7 +2357,7 @@
       <c r="L6" s="98">
         <v>46491</v>
       </c>
-      <c r="M6" s="102">
+      <c r="M6" s="30">
         <v>835100</v>
       </c>
       <c r="O6" s="15"/>
@@ -2322,7 +2367,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B7" s="104" t="s">
+      <c r="B7" s="102" t="s">
         <v>158</v>
       </c>
       <c r="C7" s="18" t="s">
@@ -2353,7 +2398,7 @@
         <v>46648</v>
       </c>
       <c r="L7" s="98"/>
-      <c r="M7" s="102"/>
+      <c r="M7" s="30"/>
       <c r="O7" s="15"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.4">
@@ -2361,7 +2406,7 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B8" s="104" t="s">
+      <c r="B8" s="102" t="s">
         <v>159</v>
       </c>
       <c r="C8" s="18" t="s">
@@ -2392,7 +2437,7 @@
         <v>46645</v>
       </c>
       <c r="L8" s="98"/>
-      <c r="M8" s="102"/>
+      <c r="M8" s="30"/>
       <c r="O8" s="15"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.4">
@@ -2400,7 +2445,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B9" s="104" t="s">
+      <c r="B9" s="102" t="s">
         <v>160</v>
       </c>
       <c r="C9" s="18" t="s">
@@ -2431,7 +2476,7 @@
         <v>46531</v>
       </c>
       <c r="L9" s="98"/>
-      <c r="M9" s="102"/>
+      <c r="M9" s="30"/>
       <c r="O9" s="15"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.4">
@@ -2439,7 +2484,7 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B10" s="104" t="s">
+      <c r="B10" s="102" t="s">
         <v>161</v>
       </c>
       <c r="C10" s="18" t="s">
@@ -2470,7 +2515,7 @@
         <v>46338</v>
       </c>
       <c r="L10" s="98"/>
-      <c r="M10" s="102"/>
+      <c r="M10" s="30"/>
       <c r="O10" s="15"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.4">
@@ -2478,7 +2523,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B11" s="104" t="s">
+      <c r="B11" s="102" t="s">
         <v>162</v>
       </c>
       <c r="C11" s="35" t="s">
@@ -2509,7 +2554,7 @@
         <v>46554</v>
       </c>
       <c r="L11" s="99"/>
-      <c r="M11" s="103"/>
+      <c r="M11" s="116"/>
       <c r="O11" s="15"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.4">
@@ -2517,7 +2562,7 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B12" s="104" t="s">
+      <c r="B12" s="102" t="s">
         <v>163</v>
       </c>
       <c r="C12" s="23" t="s">
@@ -2550,7 +2595,7 @@
       <c r="L12" s="100">
         <v>46744</v>
       </c>
-      <c r="M12" s="101">
+      <c r="M12" s="115">
         <v>763400</v>
       </c>
       <c r="O12" s="15"/>
@@ -2560,7 +2605,7 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B13" s="104" t="s">
+      <c r="B13" s="102" t="s">
         <v>164</v>
       </c>
       <c r="C13" s="18" t="s">
@@ -2593,7 +2638,7 @@
       <c r="L13" s="98">
         <v>47847</v>
       </c>
-      <c r="M13" s="102">
+      <c r="M13" s="30">
         <v>988350</v>
       </c>
       <c r="O13" s="15"/>
@@ -2603,27 +2648,49 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B14" s="105"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="18"/>
-      <c r="K14" s="26"/>
-      <c r="L14" s="28"/>
-      <c r="M14" s="30"/>
+      <c r="B14" s="102" t="s">
+        <v>227</v>
+      </c>
+      <c r="C14" s="114" t="s">
+        <v>228</v>
+      </c>
+      <c r="D14" s="114" t="s">
+        <v>229</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="G14" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="H14" s="26" t="s">
+        <v>233</v>
+      </c>
+      <c r="I14" s="103" t="s">
+        <v>234</v>
+      </c>
+      <c r="J14" s="29">
+        <v>47903</v>
+      </c>
+      <c r="K14" s="28">
+        <v>46807</v>
+      </c>
+      <c r="L14" s="29">
+        <v>47903</v>
+      </c>
+      <c r="M14" s="30">
+        <v>593297</v>
+      </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A15" s="14">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B15" s="105"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
+      <c r="B15" s="103"/>
       <c r="E15" s="18"/>
       <c r="F15" s="19"/>
       <c r="G15" s="26"/>
@@ -2639,9 +2706,7 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B16" s="105"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
+      <c r="B16" s="103"/>
       <c r="E16" s="18"/>
       <c r="F16" s="19"/>
       <c r="G16" s="26"/>
@@ -2657,9 +2722,7 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B17" s="105"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
+      <c r="B17" s="103"/>
       <c r="E17" s="18"/>
       <c r="F17" s="19"/>
       <c r="G17" s="26"/>
@@ -2672,7 +2735,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B2 B3:B13 A3:A17 B14:E17 C2:E13 F2:G17 J2:M17">
+  <conditionalFormatting sqref="C2:E13 F2:G17 E14:E17 A2:B17 C14:D14 J2:M17">
     <cfRule type="expression" dxfId="9" priority="11">
       <formula>OR(#REF!="매각",#REF!="폐기",#REF!="계약종료")</formula>
     </cfRule>
@@ -2704,15 +2767,9 @@
       <formula>#REF!="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C14:C17">
-      <formula1>구분</formula1>
-    </dataValidation>
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B15:B17">
       <formula1>사업장명</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D14:D17">
-      <formula1>차종</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2777,7 +2834,7 @@
       <c r="D2" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="102">
+      <c r="E2" s="101">
         <v>126611</v>
       </c>
       <c r="F2" s="33" t="s">
@@ -2801,7 +2858,7 @@
       <c r="D3" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="102">
+      <c r="E3" s="101">
         <v>130000</v>
       </c>
       <c r="F3" s="8" t="s">
@@ -2825,7 +2882,7 @@
       <c r="D4" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="115">
+      <c r="E4" s="104">
         <v>76000</v>
       </c>
       <c r="F4" s="8" t="s">
@@ -2851,7 +2908,7 @@
       <c r="D5" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E5" s="115">
+      <c r="E5" s="104">
         <v>39000</v>
       </c>
       <c r="F5" s="8" t="s">
@@ -2875,7 +2932,7 @@
       <c r="D6" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E6" s="115">
+      <c r="E6" s="104">
         <v>137935</v>
       </c>
       <c r="F6" s="8" t="s">
@@ -2899,7 +2956,7 @@
       <c r="D7" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="E7" s="115">
+      <c r="E7" s="104">
         <v>40000</v>
       </c>
       <c r="F7" s="8" t="s">
@@ -2923,7 +2980,7 @@
       <c r="D8" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="115">
+      <c r="E8" s="104">
         <v>35734</v>
       </c>
       <c r="F8" s="8" t="s">
@@ -2947,7 +3004,7 @@
       <c r="D9" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="115">
+      <c r="E9" s="104">
         <v>136233</v>
       </c>
       <c r="F9" s="8" t="s">
@@ -2971,7 +3028,7 @@
       <c r="D10" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="E10" s="115">
+      <c r="E10" s="104">
         <v>50000</v>
       </c>
       <c r="F10" s="8" t="s">
@@ -2995,7 +3052,7 @@
       <c r="D11" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="E11" s="115">
+      <c r="E11" s="104">
         <v>68243</v>
       </c>
       <c r="F11" s="8" t="s">
@@ -3011,7 +3068,7 @@
       <c r="B12" s="10"/>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
-      <c r="E12" s="115"/>
+      <c r="E12" s="104"/>
       <c r="F12" s="8"/>
       <c r="G12" s="9"/>
       <c r="H12" s="8"/>
@@ -3021,7 +3078,7 @@
       <c r="B13" s="10"/>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
-      <c r="E13" s="115"/>
+      <c r="E13" s="104"/>
       <c r="F13" s="8"/>
       <c r="G13" s="9"/>
       <c r="H13" s="8"/>
@@ -3031,7 +3088,7 @@
       <c r="B14" s="10"/>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
-      <c r="E14" s="115"/>
+      <c r="E14" s="104"/>
       <c r="F14" s="8"/>
       <c r="G14" s="9"/>
       <c r="H14" s="8"/>
@@ -3041,7 +3098,7 @@
       <c r="B15" s="10"/>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
-      <c r="E15" s="115"/>
+      <c r="E15" s="104"/>
       <c r="F15" s="8"/>
       <c r="G15" s="9"/>
       <c r="H15" s="8"/>
@@ -3051,7 +3108,7 @@
       <c r="B16" s="10"/>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
-      <c r="E16" s="115"/>
+      <c r="E16" s="104"/>
       <c r="F16" s="8"/>
       <c r="G16" s="9"/>
       <c r="H16" s="8"/>
@@ -3061,7 +3118,7 @@
       <c r="B17" s="10"/>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
-      <c r="E17" s="115"/>
+      <c r="E17" s="104"/>
       <c r="F17" s="8"/>
       <c r="G17" s="9"/>
       <c r="H17" s="8"/>
@@ -3071,7 +3128,7 @@
       <c r="B18" s="10"/>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
-      <c r="E18" s="115"/>
+      <c r="E18" s="104"/>
       <c r="F18" s="8"/>
       <c r="G18" s="9"/>
       <c r="H18" s="8"/>
@@ -3081,7 +3138,7 @@
       <c r="B19" s="10"/>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
-      <c r="E19" s="115"/>
+      <c r="E19" s="104"/>
       <c r="F19" s="8"/>
       <c r="G19" s="9"/>
       <c r="H19" s="8"/>
@@ -3091,7 +3148,7 @@
       <c r="B20" s="10"/>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
-      <c r="E20" s="115"/>
+      <c r="E20" s="104"/>
       <c r="F20" s="8"/>
       <c r="G20" s="9"/>
       <c r="H20" s="8"/>
@@ -3101,7 +3158,7 @@
       <c r="B21" s="10"/>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
-      <c r="E21" s="115"/>
+      <c r="E21" s="104"/>
       <c r="F21" s="8"/>
       <c r="G21" s="9"/>
       <c r="H21" s="8"/>
@@ -3111,7 +3168,7 @@
       <c r="B22" s="10"/>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
-      <c r="E22" s="115"/>
+      <c r="E22" s="104"/>
       <c r="F22" s="8"/>
       <c r="G22" s="9"/>
       <c r="H22" s="8"/>
@@ -3121,7 +3178,7 @@
       <c r="B23" s="10"/>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
-      <c r="E23" s="115"/>
+      <c r="E23" s="104"/>
       <c r="F23" s="8"/>
       <c r="G23" s="9"/>
       <c r="H23" s="8"/>
@@ -3131,7 +3188,7 @@
       <c r="B24" s="10"/>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
-      <c r="E24" s="115"/>
+      <c r="E24" s="104"/>
       <c r="F24" s="8"/>
       <c r="G24" s="9"/>
       <c r="H24" s="8"/>
@@ -3141,7 +3198,7 @@
       <c r="B25" s="10"/>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
-      <c r="E25" s="115"/>
+      <c r="E25" s="104"/>
       <c r="F25" s="8"/>
       <c r="G25" s="9"/>
       <c r="H25" s="8"/>
@@ -3151,7 +3208,7 @@
       <c r="B26" s="10"/>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
-      <c r="E26" s="115"/>
+      <c r="E26" s="104"/>
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
       <c r="H26" s="8"/>
@@ -3161,7 +3218,7 @@
       <c r="B27" s="10"/>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
-      <c r="E27" s="115"/>
+      <c r="E27" s="104"/>
       <c r="F27" s="8"/>
       <c r="G27" s="9"/>
       <c r="H27" s="8"/>
@@ -3171,7 +3228,7 @@
       <c r="B28" s="10"/>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
-      <c r="E28" s="115"/>
+      <c r="E28" s="104"/>
       <c r="F28" s="8"/>
       <c r="G28" s="9"/>
       <c r="H28" s="8"/>
@@ -3181,7 +3238,7 @@
       <c r="B29" s="10"/>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
-      <c r="E29" s="115"/>
+      <c r="E29" s="104"/>
       <c r="F29" s="8"/>
       <c r="G29" s="9"/>
       <c r="H29" s="8"/>
@@ -3191,7 +3248,7 @@
       <c r="B30" s="10"/>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
-      <c r="E30" s="115"/>
+      <c r="E30" s="104"/>
       <c r="F30" s="8"/>
       <c r="G30" s="9"/>
       <c r="H30" s="8"/>
@@ -3201,7 +3258,7 @@
       <c r="B31" s="10"/>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
-      <c r="E31" s="115"/>
+      <c r="E31" s="104"/>
       <c r="F31" s="8"/>
       <c r="G31" s="9"/>
       <c r="H31" s="8"/>
@@ -3211,7 +3268,7 @@
       <c r="B32" s="10"/>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
-      <c r="E32" s="115"/>
+      <c r="E32" s="104"/>
       <c r="F32" s="8"/>
       <c r="G32" s="9"/>
       <c r="H32" s="8"/>
@@ -3221,7 +3278,7 @@
       <c r="B33" s="10"/>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
-      <c r="E33" s="115"/>
+      <c r="E33" s="104"/>
       <c r="F33" s="8"/>
       <c r="G33" s="9"/>
       <c r="H33" s="8"/>
@@ -3231,7 +3288,7 @@
       <c r="B34" s="10"/>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
-      <c r="E34" s="115"/>
+      <c r="E34" s="104"/>
       <c r="F34" s="8"/>
       <c r="G34" s="9"/>
       <c r="H34" s="8"/>
@@ -3241,7 +3298,7 @@
       <c r="B35" s="10"/>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
-      <c r="E35" s="115"/>
+      <c r="E35" s="104"/>
       <c r="F35" s="8"/>
       <c r="G35" s="9"/>
       <c r="H35" s="8"/>
@@ -3251,7 +3308,7 @@
       <c r="B36" s="10"/>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
-      <c r="E36" s="115"/>
+      <c r="E36" s="104"/>
       <c r="F36" s="8"/>
       <c r="G36" s="9"/>
       <c r="H36" s="8"/>
@@ -3261,7 +3318,7 @@
       <c r="B37" s="10"/>
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
-      <c r="E37" s="115"/>
+      <c r="E37" s="104"/>
       <c r="F37" s="8"/>
       <c r="G37" s="9"/>
       <c r="H37" s="8"/>
@@ -3271,7 +3328,7 @@
       <c r="B38" s="10"/>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
-      <c r="E38" s="115"/>
+      <c r="E38" s="104"/>
       <c r="F38" s="8"/>
       <c r="G38" s="9"/>
       <c r="H38" s="8"/>
@@ -3877,10 +3934,10 @@
   </cols>
   <sheetData>
     <row r="9" spans="3:35" x14ac:dyDescent="0.4">
-      <c r="AA9" s="113" t="s">
+      <c r="AA9" s="112" t="s">
         <v>116</v>
       </c>
-      <c r="AB9" s="111" t="s">
+      <c r="AB9" s="110" t="s">
         <v>70</v>
       </c>
       <c r="AC9" s="67"/>
@@ -3965,8 +4022,8 @@
       <c r="Y10" s="68" t="s">
         <v>115</v>
       </c>
-      <c r="AA10" s="114"/>
-      <c r="AB10" s="112"/>
+      <c r="AA10" s="113"/>
+      <c r="AB10" s="111"/>
       <c r="AC10" s="72"/>
       <c r="AD10" s="48" t="s">
         <v>36</v>
@@ -4007,7 +4064,7 @@
         <v>45712</v>
       </c>
       <c r="I11" s="92"/>
-      <c r="K11" s="110" t="s">
+      <c r="K11" s="109" t="s">
         <v>93</v>
       </c>
       <c r="L11" s="41" t="s">
@@ -4097,7 +4154,7 @@
         <v>43727</v>
       </c>
       <c r="I12" s="92"/>
-      <c r="K12" s="110"/>
+      <c r="K12" s="109"/>
       <c r="L12" s="41" t="s">
         <v>96</v>
       </c>
@@ -4146,7 +4203,7 @@
         <v>44090</v>
       </c>
       <c r="I13" s="92"/>
-      <c r="K13" s="110"/>
+      <c r="K13" s="109"/>
       <c r="L13" s="41" t="s">
         <v>97</v>
       </c>
@@ -4204,7 +4261,7 @@
         <v>44341</v>
       </c>
       <c r="I14" s="92"/>
-      <c r="K14" s="106"/>
+      <c r="K14" s="105"/>
       <c r="L14" s="43" t="s">
         <v>98</v>
       </c>
@@ -4612,11 +4669,11 @@
       <c r="I26" s="49"/>
     </row>
     <row r="27" spans="3:35" x14ac:dyDescent="0.4">
-      <c r="C27" s="108" t="s">
+      <c r="C27" s="107" t="s">
         <v>91</v>
       </c>
-      <c r="D27" s="109"/>
-      <c r="E27" s="109"/>
+      <c r="D27" s="108"/>
+      <c r="E27" s="108"/>
       <c r="F27" s="53">
         <f>SUM(F21:F26)</f>
         <v>1200850</v>
@@ -4824,11 +4881,11 @@
       <c r="K36" s="58"/>
     </row>
     <row r="37" spans="3:11" x14ac:dyDescent="0.4">
-      <c r="C37" s="106" t="s">
+      <c r="C37" s="105" t="s">
         <v>91</v>
       </c>
-      <c r="D37" s="107"/>
-      <c r="E37" s="107"/>
+      <c r="D37" s="106"/>
+      <c r="E37" s="106"/>
       <c r="F37" s="44">
         <f>SUM(F31:F36)</f>
         <v>359030</v>

--- a/data/듀링 법인차량 현황 ver.2.0.xlsx
+++ b/data/듀링 법인차량 현황 ver.2.0.xlsx
@@ -1654,6 +1654,15 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1680,15 +1689,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2185,7 +2185,7 @@
       <c r="L2" s="25">
         <v>46836</v>
       </c>
-      <c r="M2" s="115">
+      <c r="M2" s="106">
         <v>1957670</v>
       </c>
       <c r="O2" s="15"/>
@@ -2223,7 +2223,7 @@
         <v>46408</v>
       </c>
       <c r="K3" s="28">
-        <v>46040</v>
+        <v>46405</v>
       </c>
       <c r="L3" s="29">
         <v>46408</v>
@@ -2352,7 +2352,7 @@
         <v>46491</v>
       </c>
       <c r="K6" s="28">
-        <v>46123</v>
+        <v>46488</v>
       </c>
       <c r="L6" s="98">
         <v>46491</v>
@@ -2554,7 +2554,7 @@
         <v>46554</v>
       </c>
       <c r="L11" s="99"/>
-      <c r="M11" s="116"/>
+      <c r="M11" s="107"/>
       <c r="O11" s="15"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.4">
@@ -2595,7 +2595,7 @@
       <c r="L12" s="100">
         <v>46744</v>
       </c>
-      <c r="M12" s="115">
+      <c r="M12" s="106">
         <v>763400</v>
       </c>
       <c r="O12" s="15"/>
@@ -2651,10 +2651,10 @@
       <c r="B14" s="102" t="s">
         <v>227</v>
       </c>
-      <c r="C14" s="114" t="s">
+      <c r="C14" s="105" t="s">
         <v>228</v>
       </c>
-      <c r="D14" s="114" t="s">
+      <c r="D14" s="105" t="s">
         <v>229</v>
       </c>
       <c r="E14" s="18" t="s">
@@ -3934,10 +3934,10 @@
   </cols>
   <sheetData>
     <row r="9" spans="3:35" x14ac:dyDescent="0.4">
-      <c r="AA9" s="112" t="s">
+      <c r="AA9" s="115" t="s">
         <v>116</v>
       </c>
-      <c r="AB9" s="110" t="s">
+      <c r="AB9" s="113" t="s">
         <v>70</v>
       </c>
       <c r="AC9" s="67"/>
@@ -4022,8 +4022,8 @@
       <c r="Y10" s="68" t="s">
         <v>115</v>
       </c>
-      <c r="AA10" s="113"/>
-      <c r="AB10" s="111"/>
+      <c r="AA10" s="116"/>
+      <c r="AB10" s="114"/>
       <c r="AC10" s="72"/>
       <c r="AD10" s="48" t="s">
         <v>36</v>
@@ -4064,7 +4064,7 @@
         <v>45712</v>
       </c>
       <c r="I11" s="92"/>
-      <c r="K11" s="109" t="s">
+      <c r="K11" s="112" t="s">
         <v>93</v>
       </c>
       <c r="L11" s="41" t="s">
@@ -4154,7 +4154,7 @@
         <v>43727</v>
       </c>
       <c r="I12" s="92"/>
-      <c r="K12" s="109"/>
+      <c r="K12" s="112"/>
       <c r="L12" s="41" t="s">
         <v>96</v>
       </c>
@@ -4203,7 +4203,7 @@
         <v>44090</v>
       </c>
       <c r="I13" s="92"/>
-      <c r="K13" s="109"/>
+      <c r="K13" s="112"/>
       <c r="L13" s="41" t="s">
         <v>97</v>
       </c>
@@ -4261,7 +4261,7 @@
         <v>44341</v>
       </c>
       <c r="I14" s="92"/>
-      <c r="K14" s="105"/>
+      <c r="K14" s="108"/>
       <c r="L14" s="43" t="s">
         <v>98</v>
       </c>
@@ -4669,11 +4669,11 @@
       <c r="I26" s="49"/>
     </row>
     <row r="27" spans="3:35" x14ac:dyDescent="0.4">
-      <c r="C27" s="107" t="s">
+      <c r="C27" s="110" t="s">
         <v>91</v>
       </c>
-      <c r="D27" s="108"/>
-      <c r="E27" s="108"/>
+      <c r="D27" s="111"/>
+      <c r="E27" s="111"/>
       <c r="F27" s="53">
         <f>SUM(F21:F26)</f>
         <v>1200850</v>
@@ -4881,11 +4881,11 @@
       <c r="K36" s="58"/>
     </row>
     <row r="37" spans="3:11" x14ac:dyDescent="0.4">
-      <c r="C37" s="105" t="s">
+      <c r="C37" s="108" t="s">
         <v>91</v>
       </c>
-      <c r="D37" s="106"/>
-      <c r="E37" s="106"/>
+      <c r="D37" s="109"/>
+      <c r="E37" s="109"/>
       <c r="F37" s="44">
         <f>SUM(F31:F36)</f>
         <v>359030</v>

--- a/data/듀링 법인차량 현황 ver.2.0.xlsx
+++ b/data/듀링 법인차량 현황 ver.2.0.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12444" windowHeight="10500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="12444" windowHeight="10500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="법인차량현황" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="236">
   <si>
     <t>차종</t>
   </si>
@@ -991,6 +991,10 @@
   </si>
   <si>
     <t>1544-8600</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>뒷 타이어 교체</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1696,7 +1700,35 @@
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="14">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2736,34 +2768,34 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="C2:E13 F2:G17 E14:E17 A2:B17 C14:D14 J2:M17">
-    <cfRule type="expression" dxfId="9" priority="11">
+    <cfRule type="expression" dxfId="13" priority="11">
       <formula>OR(#REF!="매각",#REF!="폐기",#REF!="계약종료")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="12">
+    <cfRule type="expression" dxfId="12" priority="12">
       <formula>#REF!="YES"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H15:I17">
-    <cfRule type="expression" dxfId="7" priority="5">
+    <cfRule type="expression" dxfId="11" priority="5">
       <formula>OR(#REF!="매각",#REF!="폐기",#REF!="계약종료")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="6">
+    <cfRule type="expression" dxfId="10" priority="6">
       <formula>#REF!="YES"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H14:I14 H2:H13">
-    <cfRule type="expression" dxfId="5" priority="3">
+    <cfRule type="expression" dxfId="9" priority="3">
       <formula>OR(#REF!="매각",#REF!="폐기",#REF!="계약종료")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="8" priority="4">
       <formula>#REF!="YES"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I13">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>OR(#REF!="매각",#REF!="폐기",#REF!="계약종료")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>#REF!="YES"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3064,13 +3096,27 @@
       <c r="H11" s="8"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="9"/>
+      <c r="A12" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B12" s="102" t="s">
+        <v>162</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>210</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="E12" s="104">
+        <v>175843</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" s="9">
+        <v>350000</v>
+      </c>
       <c r="H12" s="8"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.4">
@@ -3893,15 +3939,31 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="C11">
-    <cfRule type="expression" dxfId="1" priority="3">
+    <cfRule type="expression" dxfId="5" priority="7">
       <formula>OR(#REF!="매각",#REF!="폐기",#REF!="계약종료")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="4">
+    <cfRule type="expression" dxfId="4" priority="8">
+      <formula>#REF!="YES"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C12">
+    <cfRule type="expression" dxfId="3" priority="3">
+      <formula>OR(#REF!="매각",#REF!="폐기",#REF!="계약종료")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="4">
+      <formula>#REF!="YES"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>OR(#REF!="매각",#REF!="폐기",#REF!="계약종료")</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>#REF!="YES"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C12:C92 C2:C10">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C10 C13:C92">
       <formula1>차량번호</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/듀링 법인차량 현황 ver.2.0.xlsx
+++ b/data/듀링 법인차량 현황 ver.2.0.xlsx
@@ -3099,7 +3099,7 @@
       <c r="A12" s="10">
         <v>46105</v>
       </c>
-      <c r="B12" s="102" t="s">
+      <c r="B12" s="22" t="s">
         <v>162</v>
       </c>
       <c r="C12" s="35" t="s">

--- a/data/듀링 법인차량 현황 ver.2.0.xlsx
+++ b/data/듀링 법인차량 현황 ver.2.0.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\듀링_법인차량_QR앱패키지_ver2\during_car_qr_app_v2\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\during-car-qr-main\during-car-qr-main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1C601CD-2844-4AC5-94D9-C76EEBCAF0D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12444" windowHeight="10500" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="법인차량현황" sheetId="1" r:id="rId1"/>
@@ -27,7 +28,7 @@
     <definedName name="차량번호">OFFSET(법인차량현황!#REF!,1,0,COUNTA(법인차량현황!#REF!)-1,1)</definedName>
     <definedName name="차종">OFFSET(분류항목!$J$2,1,0,COUNTA(분류항목!$J:$J)-1,1)</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1001,7 +1002,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="#,##0&quot; 원&quot;"/>
@@ -1342,7 +1343,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1460,14 +1461,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1478,49 +1473,31 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
@@ -1550,16 +1527,16 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1">
@@ -1568,64 +1545,49 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="6" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1637,28 +1599,16 @@
     <xf numFmtId="41" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
@@ -1685,7 +1635,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1700,49 +1650,7 @@
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <fill>
         <patternFill>
@@ -2113,7 +2021,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
@@ -2184,7 +2092,7 @@
         <f>ROW()-1</f>
         <v>1</v>
       </c>
-      <c r="B2" s="102" t="s">
+      <c r="B2" s="23" t="s">
         <v>153</v>
       </c>
       <c r="C2" s="23" t="s">
@@ -2217,7 +2125,7 @@
       <c r="L2" s="25">
         <v>46836</v>
       </c>
-      <c r="M2" s="106">
+      <c r="M2" s="89">
         <v>1957670</v>
       </c>
       <c r="O2" s="15"/>
@@ -2227,7 +2135,7 @@
         <f t="shared" ref="A3:A17" si="0">ROW()-1</f>
         <v>2</v>
       </c>
-      <c r="B3" s="102" t="s">
+      <c r="B3" s="23" t="s">
         <v>154</v>
       </c>
       <c r="C3" s="18" t="s">
@@ -2270,7 +2178,7 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B4" s="102" t="s">
+      <c r="B4" s="23" t="s">
         <v>155</v>
       </c>
       <c r="C4" s="18" t="s">
@@ -2294,13 +2202,13 @@
       <c r="I4" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="J4" s="98">
+      <c r="J4" s="29">
         <v>46520</v>
       </c>
       <c r="K4" s="28">
         <v>46151</v>
       </c>
-      <c r="L4" s="98">
+      <c r="L4" s="29">
         <v>46520</v>
       </c>
       <c r="M4" s="30">
@@ -2313,7 +2221,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B5" s="102" t="s">
+      <c r="B5" s="23" t="s">
         <v>156</v>
       </c>
       <c r="C5" s="18" t="s">
@@ -2337,13 +2245,13 @@
       <c r="I5" s="23" t="s">
         <v>189</v>
       </c>
-      <c r="J5" s="98">
+      <c r="J5" s="29">
         <v>46474</v>
       </c>
       <c r="K5" s="28">
-        <v>46109</v>
-      </c>
-      <c r="L5" s="98">
+        <v>46474</v>
+      </c>
+      <c r="L5" s="29">
         <v>46474</v>
       </c>
       <c r="M5" s="30">
@@ -2356,7 +2264,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B6" s="102" t="s">
+      <c r="B6" s="23" t="s">
         <v>157</v>
       </c>
       <c r="C6" s="18" t="s">
@@ -2380,13 +2288,13 @@
       <c r="I6" s="23" t="s">
         <v>192</v>
       </c>
-      <c r="J6" s="98">
+      <c r="J6" s="29">
         <v>46491</v>
       </c>
       <c r="K6" s="28">
         <v>46488</v>
       </c>
-      <c r="L6" s="98">
+      <c r="L6" s="29">
         <v>46491</v>
       </c>
       <c r="M6" s="30">
@@ -2399,7 +2307,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B7" s="102" t="s">
+      <c r="B7" s="23" t="s">
         <v>158</v>
       </c>
       <c r="C7" s="18" t="s">
@@ -2423,13 +2331,13 @@
       <c r="I7" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="J7" s="98">
+      <c r="J7" s="29">
         <v>46168</v>
       </c>
       <c r="K7" s="28">
         <v>46648</v>
       </c>
-      <c r="L7" s="98"/>
+      <c r="L7" s="29"/>
       <c r="M7" s="30"/>
       <c r="O7" s="15"/>
     </row>
@@ -2438,7 +2346,7 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B8" s="102" t="s">
+      <c r="B8" s="23" t="s">
         <v>159</v>
       </c>
       <c r="C8" s="18" t="s">
@@ -2462,13 +2370,13 @@
       <c r="I8" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="J8" s="98">
+      <c r="J8" s="29">
         <v>46403</v>
       </c>
       <c r="K8" s="28">
         <v>46645</v>
       </c>
-      <c r="L8" s="98"/>
+      <c r="L8" s="29"/>
       <c r="M8" s="30"/>
       <c r="O8" s="15"/>
     </row>
@@ -2477,7 +2385,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B9" s="102" t="s">
+      <c r="B9" s="23" t="s">
         <v>160</v>
       </c>
       <c r="C9" s="18" t="s">
@@ -2501,13 +2409,13 @@
       <c r="I9" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="J9" s="98">
+      <c r="J9" s="29">
         <v>46166</v>
       </c>
       <c r="K9" s="28">
         <v>46531</v>
       </c>
-      <c r="L9" s="98"/>
+      <c r="L9" s="29"/>
       <c r="M9" s="30"/>
       <c r="O9" s="15"/>
     </row>
@@ -2516,7 +2424,7 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B10" s="102" t="s">
+      <c r="B10" s="23" t="s">
         <v>161</v>
       </c>
       <c r="C10" s="18" t="s">
@@ -2540,13 +2448,13 @@
       <c r="I10" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="J10" s="98">
+      <c r="J10" s="29">
         <v>46408</v>
       </c>
       <c r="K10" s="28">
         <v>46338</v>
       </c>
-      <c r="L10" s="98"/>
+      <c r="L10" s="29"/>
       <c r="M10" s="30"/>
       <c r="O10" s="15"/>
     </row>
@@ -2555,7 +2463,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B11" s="102" t="s">
+      <c r="B11" s="23" t="s">
         <v>162</v>
       </c>
       <c r="C11" s="35" t="s">
@@ -2579,14 +2487,14 @@
       <c r="I11" s="23" t="s">
         <v>195</v>
       </c>
-      <c r="J11" s="99">
+      <c r="J11" s="85">
         <v>46210</v>
       </c>
       <c r="K11" s="36">
         <v>46554</v>
       </c>
-      <c r="L11" s="99"/>
-      <c r="M11" s="107"/>
+      <c r="L11" s="85"/>
+      <c r="M11" s="90"/>
       <c r="O11" s="15"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.4">
@@ -2594,7 +2502,7 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B12" s="102" t="s">
+      <c r="B12" s="23" t="s">
         <v>163</v>
       </c>
       <c r="C12" s="23" t="s">
@@ -2618,16 +2526,16 @@
       <c r="I12" s="23" t="s">
         <v>196</v>
       </c>
-      <c r="J12" s="100">
+      <c r="J12" s="25">
         <v>46744</v>
       </c>
       <c r="K12" s="24">
         <v>46744</v>
       </c>
-      <c r="L12" s="100">
+      <c r="L12" s="25">
         <v>46744</v>
       </c>
-      <c r="M12" s="106">
+      <c r="M12" s="89">
         <v>763400</v>
       </c>
       <c r="O12" s="15"/>
@@ -2637,7 +2545,7 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B13" s="102" t="s">
+      <c r="B13" s="23" t="s">
         <v>164</v>
       </c>
       <c r="C13" s="18" t="s">
@@ -2661,13 +2569,13 @@
       <c r="I13" s="23" t="s">
         <v>197</v>
       </c>
-      <c r="J13" s="98">
+      <c r="J13" s="29">
         <v>47847</v>
       </c>
       <c r="K13" s="28">
         <v>46751</v>
       </c>
-      <c r="L13" s="98">
+      <c r="L13" s="29">
         <v>47847</v>
       </c>
       <c r="M13" s="30">
@@ -2680,13 +2588,13 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B14" s="102" t="s">
+      <c r="B14" s="23" t="s">
         <v>227</v>
       </c>
-      <c r="C14" s="105" t="s">
+      <c r="C14" s="88" t="s">
         <v>228</v>
       </c>
-      <c r="D14" s="105" t="s">
+      <c r="D14" s="88" t="s">
         <v>229</v>
       </c>
       <c r="E14" s="18" t="s">
@@ -2701,7 +2609,7 @@
       <c r="H14" s="26" t="s">
         <v>233</v>
       </c>
-      <c r="I14" s="103" t="s">
+      <c r="I14" s="18" t="s">
         <v>234</v>
       </c>
       <c r="J14" s="29">
@@ -2722,7 +2630,7 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B15" s="103"/>
+      <c r="B15" s="18"/>
       <c r="E15" s="18"/>
       <c r="F15" s="19"/>
       <c r="G15" s="26"/>
@@ -2738,7 +2646,7 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B16" s="103"/>
+      <c r="B16" s="18"/>
       <c r="E16" s="18"/>
       <c r="F16" s="19"/>
       <c r="G16" s="26"/>
@@ -2754,7 +2662,7 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B17" s="103"/>
+      <c r="B17" s="18"/>
       <c r="E17" s="18"/>
       <c r="F17" s="19"/>
       <c r="G17" s="26"/>
@@ -2767,40 +2675,24 @@
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C2:E13 F2:G17 E14:E17 A2:B17 C14:D14 J2:M17">
-    <cfRule type="expression" dxfId="13" priority="11">
+  <conditionalFormatting sqref="C2:E13 A2:B17 C14:D14 E14:E17">
+    <cfRule type="expression" dxfId="7" priority="11">
       <formula>OR(#REF!="매각",#REF!="폐기",#REF!="계약종료")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="12">
+    <cfRule type="expression" dxfId="6" priority="12">
       <formula>#REF!="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H15:I17">
-    <cfRule type="expression" dxfId="11" priority="5">
+  <conditionalFormatting sqref="F2:M17">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>OR(#REF!="매각",#REF!="폐기",#REF!="계약종료")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="6">
-      <formula>#REF!="YES"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H14:I14 H2:H13">
-    <cfRule type="expression" dxfId="9" priority="3">
-      <formula>OR(#REF!="매각",#REF!="폐기",#REF!="계약종료")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="4">
-      <formula>#REF!="YES"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I13">
-    <cfRule type="expression" dxfId="7" priority="1">
-      <formula>OR(#REF!="매각",#REF!="폐기",#REF!="계약종료")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>#REF!="YES"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B15:B17">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B15:B17" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>사업장명</formula1>
     </dataValidation>
   </dataValidations>
@@ -2810,7 +2702,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
@@ -2866,7 +2758,7 @@
       <c r="D2" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="101">
+      <c r="E2" s="86">
         <v>126611</v>
       </c>
       <c r="F2" s="33" t="s">
@@ -2890,7 +2782,7 @@
       <c r="D3" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="101">
+      <c r="E3" s="86">
         <v>130000</v>
       </c>
       <c r="F3" s="8" t="s">
@@ -2914,7 +2806,7 @@
       <c r="D4" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="104">
+      <c r="E4" s="87">
         <v>76000</v>
       </c>
       <c r="F4" s="8" t="s">
@@ -2940,7 +2832,7 @@
       <c r="D5" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E5" s="104">
+      <c r="E5" s="87">
         <v>39000</v>
       </c>
       <c r="F5" s="8" t="s">
@@ -2964,7 +2856,7 @@
       <c r="D6" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E6" s="104">
+      <c r="E6" s="87">
         <v>137935</v>
       </c>
       <c r="F6" s="8" t="s">
@@ -2988,7 +2880,7 @@
       <c r="D7" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="E7" s="104">
+      <c r="E7" s="87">
         <v>40000</v>
       </c>
       <c r="F7" s="8" t="s">
@@ -3012,7 +2904,7 @@
       <c r="D8" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="104">
+      <c r="E8" s="87">
         <v>35734</v>
       </c>
       <c r="F8" s="8" t="s">
@@ -3036,7 +2928,7 @@
       <c r="D9" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="104">
+      <c r="E9" s="87">
         <v>136233</v>
       </c>
       <c r="F9" s="8" t="s">
@@ -3060,7 +2952,7 @@
       <c r="D10" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="E10" s="104">
+      <c r="E10" s="87">
         <v>50000</v>
       </c>
       <c r="F10" s="8" t="s">
@@ -3084,7 +2976,7 @@
       <c r="D11" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="E11" s="104">
+      <c r="E11" s="87">
         <v>68243</v>
       </c>
       <c r="F11" s="8" t="s">
@@ -3108,7 +3000,7 @@
       <c r="D12" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="E12" s="104">
+      <c r="E12" s="87">
         <v>175843</v>
       </c>
       <c r="F12" s="8" t="s">
@@ -3124,7 +3016,7 @@
       <c r="B13" s="10"/>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
-      <c r="E13" s="104"/>
+      <c r="E13" s="87"/>
       <c r="F13" s="8"/>
       <c r="G13" s="9"/>
       <c r="H13" s="8"/>
@@ -3134,7 +3026,7 @@
       <c r="B14" s="10"/>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
-      <c r="E14" s="104"/>
+      <c r="E14" s="87"/>
       <c r="F14" s="8"/>
       <c r="G14" s="9"/>
       <c r="H14" s="8"/>
@@ -3144,7 +3036,7 @@
       <c r="B15" s="10"/>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
-      <c r="E15" s="104"/>
+      <c r="E15" s="87"/>
       <c r="F15" s="8"/>
       <c r="G15" s="9"/>
       <c r="H15" s="8"/>
@@ -3154,7 +3046,7 @@
       <c r="B16" s="10"/>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
-      <c r="E16" s="104"/>
+      <c r="E16" s="87"/>
       <c r="F16" s="8"/>
       <c r="G16" s="9"/>
       <c r="H16" s="8"/>
@@ -3164,7 +3056,7 @@
       <c r="B17" s="10"/>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
-      <c r="E17" s="104"/>
+      <c r="E17" s="87"/>
       <c r="F17" s="8"/>
       <c r="G17" s="9"/>
       <c r="H17" s="8"/>
@@ -3174,7 +3066,7 @@
       <c r="B18" s="10"/>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
-      <c r="E18" s="104"/>
+      <c r="E18" s="87"/>
       <c r="F18" s="8"/>
       <c r="G18" s="9"/>
       <c r="H18" s="8"/>
@@ -3184,7 +3076,7 @@
       <c r="B19" s="10"/>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
-      <c r="E19" s="104"/>
+      <c r="E19" s="87"/>
       <c r="F19" s="8"/>
       <c r="G19" s="9"/>
       <c r="H19" s="8"/>
@@ -3194,7 +3086,7 @@
       <c r="B20" s="10"/>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
-      <c r="E20" s="104"/>
+      <c r="E20" s="87"/>
       <c r="F20" s="8"/>
       <c r="G20" s="9"/>
       <c r="H20" s="8"/>
@@ -3204,7 +3096,7 @@
       <c r="B21" s="10"/>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
-      <c r="E21" s="104"/>
+      <c r="E21" s="87"/>
       <c r="F21" s="8"/>
       <c r="G21" s="9"/>
       <c r="H21" s="8"/>
@@ -3214,7 +3106,7 @@
       <c r="B22" s="10"/>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
-      <c r="E22" s="104"/>
+      <c r="E22" s="87"/>
       <c r="F22" s="8"/>
       <c r="G22" s="9"/>
       <c r="H22" s="8"/>
@@ -3224,7 +3116,7 @@
       <c r="B23" s="10"/>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
-      <c r="E23" s="104"/>
+      <c r="E23" s="87"/>
       <c r="F23" s="8"/>
       <c r="G23" s="9"/>
       <c r="H23" s="8"/>
@@ -3234,7 +3126,7 @@
       <c r="B24" s="10"/>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
-      <c r="E24" s="104"/>
+      <c r="E24" s="87"/>
       <c r="F24" s="8"/>
       <c r="G24" s="9"/>
       <c r="H24" s="8"/>
@@ -3244,7 +3136,7 @@
       <c r="B25" s="10"/>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
-      <c r="E25" s="104"/>
+      <c r="E25" s="87"/>
       <c r="F25" s="8"/>
       <c r="G25" s="9"/>
       <c r="H25" s="8"/>
@@ -3254,7 +3146,7 @@
       <c r="B26" s="10"/>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
-      <c r="E26" s="104"/>
+      <c r="E26" s="87"/>
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
       <c r="H26" s="8"/>
@@ -3264,7 +3156,7 @@
       <c r="B27" s="10"/>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
-      <c r="E27" s="104"/>
+      <c r="E27" s="87"/>
       <c r="F27" s="8"/>
       <c r="G27" s="9"/>
       <c r="H27" s="8"/>
@@ -3274,7 +3166,7 @@
       <c r="B28" s="10"/>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
-      <c r="E28" s="104"/>
+      <c r="E28" s="87"/>
       <c r="F28" s="8"/>
       <c r="G28" s="9"/>
       <c r="H28" s="8"/>
@@ -3284,7 +3176,7 @@
       <c r="B29" s="10"/>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
-      <c r="E29" s="104"/>
+      <c r="E29" s="87"/>
       <c r="F29" s="8"/>
       <c r="G29" s="9"/>
       <c r="H29" s="8"/>
@@ -3294,7 +3186,7 @@
       <c r="B30" s="10"/>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
-      <c r="E30" s="104"/>
+      <c r="E30" s="87"/>
       <c r="F30" s="8"/>
       <c r="G30" s="9"/>
       <c r="H30" s="8"/>
@@ -3304,7 +3196,7 @@
       <c r="B31" s="10"/>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
-      <c r="E31" s="104"/>
+      <c r="E31" s="87"/>
       <c r="F31" s="8"/>
       <c r="G31" s="9"/>
       <c r="H31" s="8"/>
@@ -3314,7 +3206,7 @@
       <c r="B32" s="10"/>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
-      <c r="E32" s="104"/>
+      <c r="E32" s="87"/>
       <c r="F32" s="8"/>
       <c r="G32" s="9"/>
       <c r="H32" s="8"/>
@@ -3324,7 +3216,7 @@
       <c r="B33" s="10"/>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
-      <c r="E33" s="104"/>
+      <c r="E33" s="87"/>
       <c r="F33" s="8"/>
       <c r="G33" s="9"/>
       <c r="H33" s="8"/>
@@ -3334,7 +3226,7 @@
       <c r="B34" s="10"/>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
-      <c r="E34" s="104"/>
+      <c r="E34" s="87"/>
       <c r="F34" s="8"/>
       <c r="G34" s="9"/>
       <c r="H34" s="8"/>
@@ -3344,7 +3236,7 @@
       <c r="B35" s="10"/>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
-      <c r="E35" s="104"/>
+      <c r="E35" s="87"/>
       <c r="F35" s="8"/>
       <c r="G35" s="9"/>
       <c r="H35" s="8"/>
@@ -3354,7 +3246,7 @@
       <c r="B36" s="10"/>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
-      <c r="E36" s="104"/>
+      <c r="E36" s="87"/>
       <c r="F36" s="8"/>
       <c r="G36" s="9"/>
       <c r="H36" s="8"/>
@@ -3364,7 +3256,7 @@
       <c r="B37" s="10"/>
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
-      <c r="E37" s="104"/>
+      <c r="E37" s="87"/>
       <c r="F37" s="8"/>
       <c r="G37" s="9"/>
       <c r="H37" s="8"/>
@@ -3374,7 +3266,7 @@
       <c r="B38" s="10"/>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
-      <c r="E38" s="104"/>
+      <c r="E38" s="87"/>
       <c r="F38" s="8"/>
       <c r="G38" s="9"/>
       <c r="H38" s="8"/>
@@ -3938,32 +3830,24 @@
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C11">
-    <cfRule type="expression" dxfId="5" priority="7">
+  <conditionalFormatting sqref="B12">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>OR(#REF!="매각",#REF!="폐기",#REF!="계약종료")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="8">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>#REF!="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C12">
-    <cfRule type="expression" dxfId="3" priority="3">
+  <conditionalFormatting sqref="C11:C12">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>OR(#REF!="매각",#REF!="폐기",#REF!="계약종료")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="4">
-      <formula>#REF!="YES"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B12">
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>OR(#REF!="매각",#REF!="폐기",#REF!="계약종료")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="0" priority="4">
       <formula>#REF!="YES"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C10 C13:C92">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C10 C13:C92" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>차량번호</formula1>
     </dataValidation>
   </dataValidations>
@@ -3973,7 +3857,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="C9:AI37"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
@@ -3996,582 +3880,580 @@
   </cols>
   <sheetData>
     <row r="9" spans="3:35" x14ac:dyDescent="0.4">
-      <c r="AA9" s="115" t="s">
+      <c r="AA9" s="98" t="s">
         <v>116</v>
       </c>
-      <c r="AB9" s="113" t="s">
+      <c r="AB9" s="96" t="s">
         <v>70</v>
       </c>
-      <c r="AC9" s="67"/>
-      <c r="AD9" s="45" t="s">
+      <c r="AC9" s="59"/>
+      <c r="AD9" s="37" t="s">
         <v>76</v>
       </c>
-      <c r="AE9" s="45" t="s">
+      <c r="AE9" s="37" t="s">
         <v>77</v>
       </c>
-      <c r="AF9" s="45" t="s">
+      <c r="AF9" s="37" t="s">
         <v>77</v>
       </c>
-      <c r="AG9" s="76" t="s">
+      <c r="AG9" s="68" t="s">
         <v>121</v>
       </c>
-      <c r="AH9" s="45" t="s">
+      <c r="AH9" s="37" t="s">
         <v>79</v>
       </c>
-      <c r="AI9" s="46" t="s">
+      <c r="AI9" s="43" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="10" spans="3:35" x14ac:dyDescent="0.4">
-      <c r="C10" s="69" t="s">
+      <c r="C10" s="61" t="s">
         <v>87</v>
       </c>
-      <c r="D10" s="70" t="s">
+      <c r="D10" s="62" t="s">
         <v>71</v>
       </c>
-      <c r="E10" s="70" t="s">
+      <c r="E10" s="62" t="s">
         <v>72</v>
       </c>
-      <c r="F10" s="70" t="s">
+      <c r="F10" s="62" t="s">
         <v>82</v>
       </c>
-      <c r="G10" s="70" t="s">
+      <c r="G10" s="62" t="s">
         <v>73</v>
       </c>
-      <c r="H10" s="71" t="s">
+      <c r="H10" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="I10" s="91"/>
-      <c r="K10" s="66" t="s">
+      <c r="I10" s="79"/>
+      <c r="K10" s="58" t="s">
         <v>92</v>
       </c>
-      <c r="L10" s="67" t="s">
+      <c r="L10" s="59" t="s">
         <v>94</v>
       </c>
-      <c r="M10" s="68" t="s">
+      <c r="M10" s="60" t="s">
         <v>99</v>
       </c>
-      <c r="O10" s="66" t="s">
+      <c r="O10" s="58" t="s">
         <v>104</v>
       </c>
-      <c r="P10" s="67" t="s">
+      <c r="P10" s="59" t="s">
         <v>106</v>
       </c>
-      <c r="Q10" s="67" t="s">
+      <c r="Q10" s="59" t="s">
         <v>107</v>
       </c>
-      <c r="R10" s="67" t="s">
+      <c r="R10" s="59" t="s">
         <v>108</v>
       </c>
-      <c r="S10" s="67" t="s">
+      <c r="S10" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="T10" s="67" t="s">
+      <c r="T10" s="59" t="s">
         <v>110</v>
       </c>
-      <c r="U10" s="67" t="s">
+      <c r="U10" s="59" t="s">
         <v>111</v>
       </c>
-      <c r="V10" s="67" t="s">
+      <c r="V10" s="59" t="s">
         <v>112</v>
       </c>
-      <c r="W10" s="67" t="s">
+      <c r="W10" s="59" t="s">
         <v>113</v>
       </c>
-      <c r="X10" s="67" t="s">
+      <c r="X10" s="59" t="s">
         <v>114</v>
       </c>
-      <c r="Y10" s="68" t="s">
+      <c r="Y10" s="60" t="s">
         <v>115</v>
       </c>
-      <c r="AA10" s="116"/>
-      <c r="AB10" s="114"/>
-      <c r="AC10" s="72"/>
-      <c r="AD10" s="48" t="s">
+      <c r="AA10" s="99"/>
+      <c r="AB10" s="97"/>
+      <c r="AC10" s="64"/>
+      <c r="AD10" t="s">
         <v>36</v>
       </c>
-      <c r="AE10" s="48" t="s">
+      <c r="AE10" t="s">
         <v>80</v>
       </c>
-      <c r="AF10" s="48" t="s">
+      <c r="AF10" t="s">
         <v>47</v>
       </c>
-      <c r="AG10" s="48" t="s">
+      <c r="AG10" t="s">
         <v>81</v>
       </c>
-      <c r="AH10" s="48" t="s">
+      <c r="AH10" t="s">
         <v>49</v>
       </c>
-      <c r="AI10" s="56" t="s">
+      <c r="AI10" s="51" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="11" spans="3:35" x14ac:dyDescent="0.4">
-      <c r="C11" s="47">
+      <c r="C11" s="44">
         <v>1</v>
       </c>
-      <c r="D11" s="48" t="s">
+      <c r="D11" t="s">
         <v>76</v>
       </c>
-      <c r="E11" s="48" t="s">
+      <c r="E11" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="48" t="s">
+      <c r="F11" t="s">
         <v>83</v>
       </c>
-      <c r="G11" s="49">
+      <c r="G11" s="45">
         <v>2497</v>
       </c>
-      <c r="H11" s="50">
+      <c r="H11" s="46">
         <v>45712</v>
       </c>
-      <c r="I11" s="92"/>
-      <c r="K11" s="112" t="s">
+      <c r="I11" s="80"/>
+      <c r="K11" s="95" t="s">
         <v>93</v>
       </c>
-      <c r="L11" s="41" t="s">
+      <c r="L11" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="M11" s="64" t="s">
+      <c r="M11" s="56" t="s">
         <v>100</v>
       </c>
-      <c r="O11" s="59" t="s">
+      <c r="O11" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="P11" s="73">
+      <c r="P11" s="65">
         <v>0.05</v>
       </c>
-      <c r="Q11" s="73">
+      <c r="Q11" s="65">
         <v>0.1</v>
       </c>
-      <c r="R11" s="73">
+      <c r="R11" s="65">
         <v>0.15</v>
       </c>
-      <c r="S11" s="73">
+      <c r="S11" s="65">
         <v>0.2</v>
       </c>
-      <c r="T11" s="73">
+      <c r="T11" s="65">
         <v>0.25</v>
       </c>
-      <c r="U11" s="73">
+      <c r="U11" s="65">
         <v>0.3</v>
       </c>
-      <c r="V11" s="73">
+      <c r="V11" s="65">
         <v>0.35</v>
       </c>
-      <c r="W11" s="73">
+      <c r="W11" s="65">
         <v>0.4</v>
       </c>
-      <c r="X11" s="73">
+      <c r="X11" s="65">
         <v>0.45</v>
       </c>
-      <c r="Y11" s="74">
+      <c r="Y11" s="66">
         <v>0.5</v>
       </c>
-      <c r="AA11" s="57">
+      <c r="AA11" s="44">
         <v>1</v>
       </c>
-      <c r="AB11" s="39" t="s">
+      <c r="AB11" t="s">
         <v>73</v>
       </c>
-      <c r="AC11" s="39" t="s">
+      <c r="AC11" t="s">
         <v>123</v>
       </c>
-      <c r="AD11" s="75">
+      <c r="AD11" s="67">
         <v>2497</v>
       </c>
-      <c r="AE11" s="48">
+      <c r="AE11">
         <v>180</v>
       </c>
-      <c r="AF11" s="55">
+      <c r="AF11">
         <v>180</v>
       </c>
-      <c r="AG11" s="77">
+      <c r="AG11" s="67">
         <v>1999</v>
       </c>
-      <c r="AH11" s="77">
+      <c r="AH11" s="67">
         <v>1591</v>
       </c>
-      <c r="AI11" s="58">
+      <c r="AI11" s="51">
         <v>110</v>
       </c>
     </row>
     <row r="12" spans="3:35" x14ac:dyDescent="0.4">
-      <c r="C12" s="47">
+      <c r="C12" s="44">
         <v>2</v>
       </c>
-      <c r="D12" s="48" t="s">
+      <c r="D12" t="s">
         <v>77</v>
       </c>
-      <c r="E12" s="48" t="s">
+      <c r="E12" t="s">
         <v>80</v>
       </c>
-      <c r="F12" s="48" t="s">
+      <c r="F12" t="s">
         <v>84</v>
       </c>
-      <c r="G12" s="49">
+      <c r="G12" s="45">
         <v>180</v>
       </c>
-      <c r="H12" s="50">
+      <c r="H12" s="46">
         <v>43727</v>
       </c>
-      <c r="I12" s="92"/>
-      <c r="K12" s="112"/>
-      <c r="L12" s="41" t="s">
+      <c r="I12" s="80"/>
+      <c r="K12" s="95"/>
+      <c r="L12" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="M12" s="64" t="s">
+      <c r="M12" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="AA12" s="57">
+      <c r="AA12" s="44">
         <v>2</v>
       </c>
-      <c r="AB12" s="39" t="s">
+      <c r="AB12" t="s">
         <v>117</v>
       </c>
-      <c r="AC12" s="39" t="s">
+      <c r="AC12" t="s">
         <v>124</v>
       </c>
-      <c r="AD12" s="48">
+      <c r="AD12">
         <v>200</v>
       </c>
-      <c r="AE12" s="48"/>
-      <c r="AF12" s="39"/>
-      <c r="AG12" s="39">
+      <c r="AG12">
         <v>200</v>
       </c>
-      <c r="AH12" s="39">
+      <c r="AH12">
         <v>140</v>
       </c>
-      <c r="AI12" s="58"/>
+      <c r="AI12" s="51"/>
     </row>
     <row r="13" spans="3:35" x14ac:dyDescent="0.4">
-      <c r="C13" s="47">
+      <c r="C13" s="44">
         <v>3</v>
       </c>
-      <c r="D13" s="48" t="s">
+      <c r="D13" t="s">
         <v>77</v>
       </c>
-      <c r="E13" s="48" t="s">
+      <c r="E13" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="48" t="s">
+      <c r="F13" t="s">
         <v>85</v>
       </c>
-      <c r="G13" s="49">
+      <c r="G13" s="45">
         <v>180</v>
       </c>
-      <c r="H13" s="50">
+      <c r="H13" s="46">
         <v>44090</v>
       </c>
-      <c r="I13" s="92"/>
-      <c r="K13" s="112"/>
-      <c r="L13" s="41" t="s">
+      <c r="I13" s="80"/>
+      <c r="K13" s="95"/>
+      <c r="L13" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="M13" s="64" t="s">
+      <c r="M13" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="AA13" s="57">
+      <c r="AA13" s="44">
         <v>3</v>
       </c>
-      <c r="AB13" s="39" t="s">
+      <c r="AB13" t="s">
         <v>118</v>
       </c>
-      <c r="AC13" s="39" t="s">
+      <c r="AC13" t="s">
         <v>125</v>
       </c>
-      <c r="AD13" s="49">
+      <c r="AD13" s="45">
         <f>AD11*AD12</f>
         <v>499400</v>
       </c>
-      <c r="AE13" s="49">
+      <c r="AE13" s="45">
         <v>100000</v>
       </c>
-      <c r="AF13" s="49">
+      <c r="AF13" s="45">
         <v>100000</v>
       </c>
-      <c r="AG13" s="49">
+      <c r="AG13" s="45">
         <f t="shared" ref="AG13:AH13" si="0">AG11*AG12</f>
         <v>399800</v>
       </c>
-      <c r="AH13" s="49">
+      <c r="AH13" s="45">
         <f t="shared" si="0"/>
         <v>222740</v>
       </c>
-      <c r="AI13" s="58">
+      <c r="AI13" s="51">
         <v>100000</v>
       </c>
     </row>
     <row r="14" spans="3:35" x14ac:dyDescent="0.4">
-      <c r="C14" s="47">
+      <c r="C14" s="44">
         <v>4</v>
       </c>
-      <c r="D14" s="48" t="s">
+      <c r="D14" t="s">
         <v>78</v>
       </c>
-      <c r="E14" s="48" t="s">
+      <c r="E14" t="s">
         <v>81</v>
       </c>
-      <c r="F14" s="48" t="s">
+      <c r="F14" t="s">
         <v>86</v>
       </c>
-      <c r="G14" s="49">
+      <c r="G14" s="45">
         <v>1999</v>
       </c>
-      <c r="H14" s="50">
+      <c r="H14" s="46">
         <v>44341</v>
       </c>
-      <c r="I14" s="92"/>
-      <c r="K14" s="108"/>
-      <c r="L14" s="43" t="s">
+      <c r="I14" s="80"/>
+      <c r="K14" s="91"/>
+      <c r="L14" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="M14" s="65" t="s">
+      <c r="M14" s="57" t="s">
         <v>103</v>
       </c>
-      <c r="AA14" s="57">
+      <c r="AA14" s="44">
         <v>4</v>
       </c>
-      <c r="AB14" s="39" t="s">
+      <c r="AB14" t="s">
         <v>119</v>
       </c>
-      <c r="AC14" s="39" t="s">
+      <c r="AC14" t="s">
         <v>126</v>
       </c>
-      <c r="AD14" s="78">
+      <c r="AD14" s="69">
         <v>1</v>
       </c>
-      <c r="AE14" s="78">
+      <c r="AE14" s="69">
         <v>1</v>
       </c>
-      <c r="AF14" s="78">
+      <c r="AF14" s="69">
         <v>1</v>
       </c>
-      <c r="AG14" s="79">
+      <c r="AG14" s="69">
         <v>0.8</v>
       </c>
-      <c r="AH14" s="79">
+      <c r="AH14" s="69">
         <v>0.6</v>
       </c>
-      <c r="AI14" s="90">
+      <c r="AI14" s="70">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="3:35" x14ac:dyDescent="0.4">
-      <c r="C15" s="47">
+      <c r="C15" s="44">
         <v>5</v>
       </c>
-      <c r="D15" s="48" t="s">
+      <c r="D15" t="s">
         <v>79</v>
       </c>
-      <c r="E15" s="48" t="s">
+      <c r="E15" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="48" t="s">
+      <c r="F15" t="s">
         <v>83</v>
       </c>
-      <c r="G15" s="49">
+      <c r="G15" s="45">
         <v>1591</v>
       </c>
-      <c r="H15" s="50">
+      <c r="H15" s="46">
         <v>43052</v>
       </c>
-      <c r="I15" s="92"/>
-      <c r="AA15" s="57">
+      <c r="I15" s="80"/>
+      <c r="AA15" s="44">
         <v>5</v>
       </c>
-      <c r="AB15" s="39" t="s">
+      <c r="AB15" t="s">
         <v>120</v>
       </c>
-      <c r="AC15" s="39" t="s">
+      <c r="AC15" t="s">
         <v>127</v>
       </c>
-      <c r="AD15" s="49">
+      <c r="AD15" s="45">
         <v>499400</v>
       </c>
-      <c r="AE15" s="49">
+      <c r="AE15" s="45">
         <v>100000</v>
       </c>
-      <c r="AF15" s="40">
+      <c r="AF15" s="39">
         <v>100000</v>
       </c>
-      <c r="AG15" s="40">
+      <c r="AG15" s="39">
         <f>399800*0.8</f>
         <v>319840</v>
       </c>
-      <c r="AH15" s="40">
+      <c r="AH15" s="39">
         <f>AH13*0.65</f>
         <v>144781</v>
       </c>
-      <c r="AI15" s="61">
+      <c r="AI15" s="53">
         <v>100000</v>
       </c>
     </row>
     <row r="16" spans="3:35" x14ac:dyDescent="0.4">
-      <c r="C16" s="51">
+      <c r="C16" s="47">
         <v>6</v>
       </c>
-      <c r="D16" s="52" t="s">
+      <c r="D16" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="E16" s="52" t="s">
+      <c r="E16" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="52" t="s">
+      <c r="F16" s="48" t="s">
         <v>85</v>
       </c>
-      <c r="G16" s="53">
+      <c r="G16" s="49">
         <v>111</v>
       </c>
-      <c r="H16" s="54">
+      <c r="H16" s="50">
         <v>44364</v>
       </c>
-      <c r="I16" s="92"/>
-      <c r="AA16" s="57">
+      <c r="I16" s="80"/>
+      <c r="AA16" s="44">
         <v>8</v>
       </c>
-      <c r="AB16" s="39" t="s">
+      <c r="AB16" t="s">
         <v>122</v>
       </c>
-      <c r="AC16" s="39" t="s">
+      <c r="AC16" t="s">
         <v>128</v>
       </c>
-      <c r="AD16" s="79">
+      <c r="AD16" s="69">
         <v>0.3</v>
       </c>
-      <c r="AE16" s="79">
+      <c r="AE16" s="69">
         <v>0.3</v>
       </c>
-      <c r="AF16" s="79">
+      <c r="AF16" s="69">
         <v>0.3</v>
       </c>
-      <c r="AG16" s="79">
+      <c r="AG16" s="69">
         <v>0.3</v>
       </c>
-      <c r="AH16" s="79">
+      <c r="AH16" s="69">
         <v>0.3</v>
       </c>
-      <c r="AI16" s="80">
+      <c r="AI16" s="70">
         <v>0.3</v>
       </c>
     </row>
     <row r="17" spans="3:35" x14ac:dyDescent="0.4">
-      <c r="AA17" s="57">
+      <c r="AA17" s="44">
         <v>9</v>
       </c>
-      <c r="AB17" s="39" t="s">
+      <c r="AB17" t="s">
         <v>132</v>
       </c>
-      <c r="AC17" s="39" t="s">
+      <c r="AC17" t="s">
         <v>129</v>
       </c>
-      <c r="AD17" s="81">
+      <c r="AD17" s="71">
         <f>AD15*0.3</f>
         <v>149820</v>
       </c>
-      <c r="AE17" s="81">
+      <c r="AE17" s="71">
         <v>30000</v>
       </c>
-      <c r="AF17" s="81">
+      <c r="AF17" s="71">
         <v>30000</v>
       </c>
-      <c r="AG17" s="81">
+      <c r="AG17" s="71">
         <f>AG15*0.3</f>
         <v>95952</v>
       </c>
-      <c r="AH17" s="81">
+      <c r="AH17" s="71">
         <f>AH15*0.3</f>
         <v>43434.299999999996</v>
       </c>
-      <c r="AI17" s="82">
+      <c r="AI17" s="72">
         <v>30000</v>
       </c>
     </row>
     <row r="18" spans="3:35" x14ac:dyDescent="0.4">
-      <c r="AA18" s="57">
+      <c r="AA18" s="44">
         <v>10</v>
       </c>
-      <c r="AB18" s="39" t="s">
+      <c r="AB18" t="s">
         <v>134</v>
       </c>
-      <c r="AC18" s="39" t="s">
+      <c r="AC18" t="s">
         <v>130</v>
       </c>
-      <c r="AD18" s="84">
+      <c r="AD18" s="74">
         <v>29710</v>
       </c>
-      <c r="AE18" s="84">
+      <c r="AE18" s="74">
         <v>5960</v>
       </c>
-      <c r="AF18" s="84">
+      <c r="AF18" s="74">
         <v>5960</v>
       </c>
-      <c r="AG18" s="84">
+      <c r="AG18" s="74">
         <v>19002</v>
       </c>
-      <c r="AH18" s="84">
+      <c r="AH18" s="74">
         <v>15525</v>
       </c>
-      <c r="AI18" s="85">
+      <c r="AI18" s="75">
         <v>5960</v>
       </c>
     </row>
     <row r="19" spans="3:35" x14ac:dyDescent="0.4">
-      <c r="AA19" s="57">
+      <c r="AA19" s="44">
         <v>11</v>
       </c>
-      <c r="AB19" s="39" t="s">
+      <c r="AB19" t="s">
         <v>133</v>
       </c>
-      <c r="AC19" s="39" t="s">
+      <c r="AC19" t="s">
         <v>131</v>
       </c>
-      <c r="AD19" s="88">
+      <c r="AD19" s="77">
         <f>AD15+AD17-AD18</f>
         <v>619510</v>
       </c>
-      <c r="AE19" s="88">
+      <c r="AE19" s="77">
         <f>AE15+AE17-AE18</f>
         <v>124040</v>
       </c>
-      <c r="AF19" s="88">
+      <c r="AF19" s="77">
         <f>AF15+AF17-AF18</f>
         <v>124040</v>
       </c>
-      <c r="AG19" s="88">
+      <c r="AG19" s="77">
         <f t="shared" ref="AG19:AH19" si="1">AG15+AG17-AG18</f>
         <v>396790</v>
       </c>
-      <c r="AH19" s="88">
+      <c r="AH19" s="77">
         <f t="shared" si="1"/>
         <v>172690.3</v>
       </c>
-      <c r="AI19" s="89">
+      <c r="AI19" s="78">
         <f>AI15+AI17-AI18</f>
         <v>124040</v>
       </c>
     </row>
     <row r="20" spans="3:35" x14ac:dyDescent="0.4">
-      <c r="C20" s="69" t="s">
+      <c r="C20" s="61" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="70" t="s">
+      <c r="D20" s="62" t="s">
         <v>71</v>
       </c>
-      <c r="E20" s="70" t="s">
+      <c r="E20" s="62" t="s">
         <v>72</v>
       </c>
-      <c r="F20" s="70" t="s">
+      <c r="F20" s="62" t="s">
         <v>89</v>
       </c>
-      <c r="G20" s="70" t="s">
+      <c r="G20" s="62" t="s">
         <v>88</v>
       </c>
-      <c r="H20" s="71" t="s">
+      <c r="H20" s="63" t="s">
         <v>90</v>
       </c>
-      <c r="I20" s="91"/>
+      <c r="I20" s="79"/>
       <c r="AA20" s="37"/>
       <c r="AB20" s="37"/>
       <c r="AC20" s="37"/>
@@ -4583,199 +4465,192 @@
       <c r="AI20" s="37"/>
     </row>
     <row r="21" spans="3:35" x14ac:dyDescent="0.4">
-      <c r="C21" s="47">
+      <c r="C21" s="44">
         <v>1</v>
       </c>
-      <c r="D21" s="48" t="s">
+      <c r="D21" t="s">
         <v>76</v>
       </c>
-      <c r="E21" s="48" t="s">
+      <c r="E21" t="s">
         <v>36</v>
       </c>
-      <c r="F21" s="49">
+      <c r="F21" s="45">
         <v>476550</v>
       </c>
-      <c r="G21" s="49">
+      <c r="G21" s="45">
         <v>142960</v>
       </c>
-      <c r="H21" s="62">
+      <c r="H21" s="54">
         <f>F21+G21</f>
         <v>619510</v>
       </c>
-      <c r="I21" s="49"/>
-      <c r="AA21" s="39"/>
-      <c r="AB21" s="39"/>
-      <c r="AC21" s="39"/>
-      <c r="AD21" s="83"/>
-      <c r="AE21" s="39"/>
-      <c r="AF21" s="39"/>
-      <c r="AG21" s="83"/>
-      <c r="AH21" s="39"/>
-      <c r="AI21" s="39"/>
+      <c r="I21" s="45"/>
+      <c r="AD21" s="73"/>
+      <c r="AG21" s="73"/>
     </row>
     <row r="22" spans="3:35" x14ac:dyDescent="0.4">
-      <c r="C22" s="47">
+      <c r="C22" s="44">
         <v>2</v>
       </c>
-      <c r="D22" s="48" t="s">
+      <c r="D22" t="s">
         <v>77</v>
       </c>
-      <c r="E22" s="48" t="s">
+      <c r="E22" t="s">
         <v>80</v>
       </c>
-      <c r="F22" s="49">
+      <c r="F22" s="45">
         <v>95420</v>
       </c>
-      <c r="G22" s="49">
+      <c r="G22" s="45">
         <v>28620</v>
       </c>
-      <c r="H22" s="62">
+      <c r="H22" s="54">
         <f t="shared" ref="H22:H27" si="2">F22+G22</f>
         <v>124040</v>
       </c>
-      <c r="I22" s="49"/>
-      <c r="AD22" s="86"/>
-      <c r="AE22" s="86"/>
-      <c r="AF22" s="86"/>
-      <c r="AG22" s="86"/>
-      <c r="AH22" s="86"/>
+      <c r="I22" s="45"/>
+      <c r="AD22" s="71"/>
+      <c r="AE22" s="71"/>
+      <c r="AF22" s="71"/>
+      <c r="AG22" s="71"/>
+      <c r="AH22" s="71"/>
     </row>
     <row r="23" spans="3:35" x14ac:dyDescent="0.4">
-      <c r="C23" s="47">
+      <c r="C23" s="44">
         <v>3</v>
       </c>
-      <c r="D23" s="48" t="s">
+      <c r="D23" t="s">
         <v>77</v>
       </c>
-      <c r="E23" s="48" t="s">
+      <c r="E23" t="s">
         <v>47</v>
       </c>
-      <c r="F23" s="49">
+      <c r="F23" s="45">
         <v>95420</v>
       </c>
-      <c r="G23" s="49">
+      <c r="G23" s="45">
         <v>28620</v>
       </c>
-      <c r="H23" s="62">
+      <c r="H23" s="54">
         <f t="shared" si="2"/>
         <v>124040</v>
       </c>
-      <c r="I23" s="49"/>
-      <c r="AH23" s="87"/>
+      <c r="I23" s="45"/>
+      <c r="AH23" s="76"/>
     </row>
     <row r="24" spans="3:35" x14ac:dyDescent="0.4">
-      <c r="C24" s="47">
+      <c r="C24" s="44">
         <v>4</v>
       </c>
-      <c r="D24" s="48" t="s">
+      <c r="D24" t="s">
         <v>78</v>
       </c>
-      <c r="E24" s="48" t="s">
+      <c r="E24" t="s">
         <v>81</v>
       </c>
-      <c r="F24" s="49">
+      <c r="F24" s="45">
         <v>305200</v>
       </c>
-      <c r="G24" s="49">
+      <c r="G24" s="45">
         <v>91560</v>
       </c>
-      <c r="H24" s="62">
+      <c r="H24" s="54">
         <f t="shared" si="2"/>
         <v>396760</v>
       </c>
-      <c r="I24" s="49"/>
-      <c r="AH24" s="87"/>
+      <c r="I24" s="45"/>
+      <c r="AH24" s="76"/>
     </row>
     <row r="25" spans="3:35" x14ac:dyDescent="0.4">
-      <c r="C25" s="47">
+      <c r="C25" s="44">
         <v>5</v>
       </c>
-      <c r="D25" s="48" t="s">
+      <c r="D25" t="s">
         <v>79</v>
       </c>
-      <c r="E25" s="48" t="s">
+      <c r="E25" t="s">
         <v>49</v>
       </c>
-      <c r="F25" s="49">
+      <c r="F25" s="45">
         <v>132840</v>
       </c>
-      <c r="G25" s="49">
+      <c r="G25" s="45">
         <v>39850</v>
       </c>
-      <c r="H25" s="62">
+      <c r="H25" s="54">
         <f t="shared" si="2"/>
         <v>172690</v>
       </c>
-      <c r="I25" s="49"/>
+      <c r="I25" s="45"/>
     </row>
     <row r="26" spans="3:35" x14ac:dyDescent="0.4">
-      <c r="C26" s="51">
+      <c r="C26" s="47">
         <v>6</v>
       </c>
-      <c r="D26" s="52" t="s">
+      <c r="D26" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="E26" s="52" t="s">
+      <c r="E26" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F26" s="53">
+      <c r="F26" s="49">
         <v>95420</v>
       </c>
-      <c r="G26" s="53">
+      <c r="G26" s="49">
         <v>28620</v>
       </c>
-      <c r="H26" s="62">
+      <c r="H26" s="54">
         <f t="shared" si="2"/>
         <v>124040</v>
       </c>
-      <c r="I26" s="49"/>
+      <c r="I26" s="45"/>
     </row>
     <row r="27" spans="3:35" x14ac:dyDescent="0.4">
-      <c r="C27" s="110" t="s">
+      <c r="C27" s="93" t="s">
         <v>91</v>
       </c>
-      <c r="D27" s="111"/>
-      <c r="E27" s="111"/>
-      <c r="F27" s="53">
+      <c r="D27" s="94"/>
+      <c r="E27" s="94"/>
+      <c r="F27" s="49">
         <f>SUM(F21:F26)</f>
         <v>1200850</v>
       </c>
-      <c r="G27" s="53">
+      <c r="G27" s="49">
         <f>SUM(G21:G26)</f>
         <v>360230</v>
       </c>
-      <c r="H27" s="63">
+      <c r="H27" s="55">
         <f t="shared" si="2"/>
         <v>1561080</v>
       </c>
-      <c r="I27" s="93"/>
+      <c r="I27" s="81"/>
     </row>
     <row r="30" spans="3:35" x14ac:dyDescent="0.4">
-      <c r="C30" s="66" t="s">
+      <c r="C30" s="58" t="s">
         <v>87</v>
       </c>
-      <c r="D30" s="67" t="s">
+      <c r="D30" s="59" t="s">
         <v>71</v>
       </c>
-      <c r="E30" s="67" t="s">
+      <c r="E30" s="59" t="s">
         <v>72</v>
       </c>
-      <c r="F30" s="67">
+      <c r="F30" s="59">
         <v>2024</v>
       </c>
-      <c r="G30" s="67">
+      <c r="G30" s="59">
         <v>2025</v>
       </c>
-      <c r="H30" s="67">
+      <c r="H30" s="59">
         <v>2026</v>
       </c>
-      <c r="I30" s="67" t="s">
+      <c r="I30" s="59" t="s">
         <v>135</v>
       </c>
-      <c r="J30" s="67" t="s">
+      <c r="J30" s="59" t="s">
         <v>136</v>
       </c>
-      <c r="K30" s="94" t="s">
+      <c r="K30" s="63" t="s">
         <v>75</v>
       </c>
     </row>
@@ -4783,27 +4658,27 @@
       <c r="C31" s="38">
         <v>1</v>
       </c>
-      <c r="D31" s="41" t="s">
+      <c r="D31" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E31" s="41" t="s">
+      <c r="E31" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F31" s="42"/>
-      <c r="G31" s="42">
+      <c r="F31" s="40"/>
+      <c r="G31" s="40">
         <f>225880+324610</f>
         <v>550490</v>
       </c>
-      <c r="H31" s="42">
+      <c r="H31" s="40">
         <v>619510</v>
       </c>
-      <c r="I31" s="97" t="s">
+      <c r="I31" s="84" t="s">
         <v>151</v>
       </c>
-      <c r="J31" s="96" t="s">
+      <c r="J31" s="83" t="s">
         <v>144</v>
       </c>
-      <c r="K31" s="58" t="s">
+      <c r="K31" s="51" t="s">
         <v>148</v>
       </c>
     </row>
@@ -4811,26 +4686,26 @@
       <c r="C32" s="38">
         <v>2</v>
       </c>
-      <c r="D32" s="41" t="s">
+      <c r="D32" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E32" s="41" t="s">
+      <c r="E32" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F32" s="42"/>
-      <c r="G32" s="42">
+      <c r="F32" s="40"/>
+      <c r="G32" s="40">
         <v>75070</v>
       </c>
-      <c r="H32" s="42">
+      <c r="H32" s="40">
         <v>124040</v>
       </c>
-      <c r="I32" s="42" t="s">
+      <c r="I32" s="40" t="s">
         <v>137</v>
       </c>
-      <c r="J32" s="41" t="s">
+      <c r="J32" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="K32" s="58" t="s">
+      <c r="K32" s="51" t="s">
         <v>149</v>
       </c>
     </row>
@@ -4838,26 +4713,26 @@
       <c r="C33" s="38">
         <v>3</v>
       </c>
-      <c r="D33" s="41" t="s">
+      <c r="D33" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E33" s="41" t="s">
+      <c r="E33" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F33" s="42"/>
-      <c r="G33" s="42">
+      <c r="F33" s="40"/>
+      <c r="G33" s="40">
         <v>121010</v>
       </c>
-      <c r="H33" s="42">
+      <c r="H33" s="40">
         <v>124040</v>
       </c>
-      <c r="I33" s="42" t="s">
+      <c r="I33" s="40" t="s">
         <v>145</v>
       </c>
-      <c r="J33" s="41" t="s">
+      <c r="J33" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="K33" s="58" t="s">
+      <c r="K33" s="51" t="s">
         <v>150</v>
       </c>
     </row>
@@ -4865,108 +4740,108 @@
       <c r="C34" s="38">
         <v>4</v>
       </c>
-      <c r="D34" s="41" t="s">
+      <c r="D34" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E34" s="41" t="s">
+      <c r="E34" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F34" s="42">
+      <c r="F34" s="40">
         <v>34680</v>
       </c>
-      <c r="G34" s="42">
+      <c r="G34" s="40">
         <v>421560</v>
       </c>
-      <c r="H34" s="42">
+      <c r="H34" s="40">
         <v>396760</v>
       </c>
-      <c r="I34" s="42" t="s">
+      <c r="I34" s="40" t="s">
         <v>140</v>
       </c>
-      <c r="J34" s="41" t="s">
+      <c r="J34" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="K34" s="58"/>
+      <c r="K34" s="51"/>
     </row>
     <row r="35" spans="3:11" x14ac:dyDescent="0.4">
       <c r="C35" s="38">
         <v>5</v>
       </c>
-      <c r="D35" s="41" t="s">
+      <c r="D35" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E35" s="41" t="s">
+      <c r="E35" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F35" s="42">
+      <c r="F35" s="40">
         <v>200310</v>
       </c>
-      <c r="G35" s="42">
+      <c r="G35" s="40">
         <v>186510</v>
       </c>
-      <c r="H35" s="42">
+      <c r="H35" s="40">
         <v>172690</v>
       </c>
-      <c r="I35" s="42" t="s">
+      <c r="I35" s="40" t="s">
         <v>142</v>
       </c>
-      <c r="J35" s="41" t="s">
+      <c r="J35" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="K35" s="58"/>
+      <c r="K35" s="51"/>
     </row>
     <row r="36" spans="3:11" x14ac:dyDescent="0.4">
       <c r="C36" s="38">
         <v>6</v>
       </c>
-      <c r="D36" s="41" t="s">
+      <c r="D36" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E36" s="41" t="s">
+      <c r="E36" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F36" s="42">
+      <c r="F36" s="40">
         <v>124040</v>
       </c>
-      <c r="G36" s="42">
+      <c r="G36" s="40">
         <v>124040</v>
       </c>
-      <c r="H36" s="42">
+      <c r="H36" s="40">
         <v>124040</v>
       </c>
-      <c r="I36" s="42">
+      <c r="I36" s="40">
         <v>0</v>
       </c>
-      <c r="J36" s="96">
+      <c r="J36" s="83">
         <v>0</v>
       </c>
-      <c r="K36" s="58"/>
+      <c r="K36" s="51"/>
     </row>
     <row r="37" spans="3:11" x14ac:dyDescent="0.4">
-      <c r="C37" s="108" t="s">
+      <c r="C37" s="91" t="s">
         <v>91</v>
       </c>
-      <c r="D37" s="109"/>
-      <c r="E37" s="109"/>
-      <c r="F37" s="44">
+      <c r="D37" s="92"/>
+      <c r="E37" s="92"/>
+      <c r="F37" s="42">
         <f>SUM(F31:F36)</f>
         <v>359030</v>
       </c>
-      <c r="G37" s="44">
+      <c r="G37" s="42">
         <f>SUM(G31:G36)</f>
         <v>1478680</v>
       </c>
-      <c r="H37" s="95">
+      <c r="H37" s="82">
         <f t="shared" ref="H37" si="3">F37+G37</f>
         <v>1837710</v>
       </c>
-      <c r="I37" s="95" t="s">
+      <c r="I37" s="82" t="s">
         <v>146</v>
       </c>
-      <c r="J37" s="95" t="s">
+      <c r="J37" s="82" t="s">
         <v>147</v>
       </c>
-      <c r="K37" s="60"/>
+      <c r="K37" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4986,7 +4861,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:J10"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>

--- a/data/듀링 법인차량 현황 ver.2.0.xlsx
+++ b/data/듀링 법인차량 현황 ver.2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\during-car-qr-main\during-car-qr-main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1C601CD-2844-4AC5-94D9-C76EEBCAF0D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD5A6F27-1BDA-4683-B70A-79B0C3A65883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="238">
   <si>
     <t>차종</t>
   </si>
@@ -836,10 +836,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>1544-0114</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>1577-0565</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -996,6 +992,18 @@
   </si>
   <si>
     <t>뒷 타이어 교체</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>타이어테크 신서산온석점</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>현대해상</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1577-1001</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2096,7 +2104,7 @@
         <v>153</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>40</v>
@@ -2139,7 +2147,7 @@
         <v>154</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D3" s="18" t="s">
         <v>39</v>
@@ -2182,7 +2190,7 @@
         <v>155</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>41</v>
@@ -2225,7 +2233,7 @@
         <v>156</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>42</v>
@@ -2268,7 +2276,7 @@
         <v>157</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>42</v>
@@ -2311,7 +2319,7 @@
         <v>158</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D7" s="19" t="s">
         <v>37</v>
@@ -2350,7 +2358,7 @@
         <v>159</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>37</v>
@@ -2389,7 +2397,7 @@
         <v>160</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D9" s="19" t="s">
         <v>42</v>
@@ -2428,7 +2436,7 @@
         <v>161</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D10" s="18" t="s">
         <v>57</v>
@@ -2467,7 +2475,7 @@
         <v>162</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D11" s="35" t="s">
         <v>58</v>
@@ -2482,10 +2490,10 @@
         <v>177</v>
       </c>
       <c r="H11" s="26" t="s">
-        <v>48</v>
+        <v>236</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>195</v>
+        <v>237</v>
       </c>
       <c r="J11" s="85">
         <v>46210</v>
@@ -2524,7 +2532,7 @@
         <v>181</v>
       </c>
       <c r="I12" s="23" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J12" s="25">
         <v>46744</v>
@@ -2567,7 +2575,7 @@
         <v>181</v>
       </c>
       <c r="I13" s="23" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J13" s="29">
         <v>47847</v>
@@ -2589,28 +2597,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="23" t="s">
+        <v>226</v>
+      </c>
+      <c r="C14" s="88" t="s">
         <v>227</v>
       </c>
-      <c r="C14" s="88" t="s">
+      <c r="D14" s="88" t="s">
         <v>228</v>
       </c>
-      <c r="D14" s="88" t="s">
+      <c r="E14" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="F14" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="G14" s="26" t="s">
         <v>230</v>
       </c>
-      <c r="F14" s="19" t="s">
+      <c r="H14" s="26" t="s">
         <v>232</v>
       </c>
-      <c r="G14" s="26" t="s">
-        <v>231</v>
-      </c>
-      <c r="H14" s="26" t="s">
+      <c r="I14" s="18" t="s">
         <v>233</v>
-      </c>
-      <c r="I14" s="18" t="s">
-        <v>234</v>
       </c>
       <c r="J14" s="29">
         <v>47903</v>
@@ -2721,22 +2729,22 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="20" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C1" s="20" t="s">
         <v>21</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E1" s="20" t="s">
         <v>22</v>
       </c>
       <c r="F1" s="20" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G1" s="20" t="s">
         <v>23</v>
@@ -2750,10 +2758,10 @@
         <v>45854</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D2" s="33" t="s">
         <v>50</v>
@@ -2774,10 +2782,10 @@
         <v>45855</v>
       </c>
       <c r="B3" s="32" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D3" s="33" t="s">
         <v>55</v>
@@ -2798,10 +2806,10 @@
         <v>45883</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>43</v>
@@ -2824,10 +2832,10 @@
         <v>45888</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>54</v>
@@ -2848,10 +2856,10 @@
         <v>45890</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>45</v>
@@ -2872,10 +2880,10 @@
         <v>45915</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>60</v>
@@ -2896,10 +2904,10 @@
         <v>45975</v>
       </c>
       <c r="B8" s="32" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>62</v>
@@ -2920,10 +2928,10 @@
         <v>46028</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>62</v>
@@ -2944,10 +2952,10 @@
         <v>46043</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>60</v>
@@ -2968,10 +2976,10 @@
         <v>46050</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>60</v>
@@ -2995,16 +3003,16 @@
         <v>162</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E12" s="87">
         <v>175843</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>61</v>
+        <v>235</v>
       </c>
       <c r="G12" s="9">
         <v>350000</v>

--- a/data/듀링 법인차량 현황 ver.2.0.xlsx
+++ b/data/듀링 법인차량 현황 ver.2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\during-car-qr-main\during-car-qr-main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD5A6F27-1BDA-4683-B70A-79B0C3A65883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA9F153F-5B6B-4EAA-ADFB-6EC4E4981CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1003,7 +1003,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>1577-1001</t>
+    <t>1588-5656</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>

--- a/data/듀링 법인차량 현황 ver.2.0.xlsx
+++ b/data/듀링 법인차량 현황 ver.2.0.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\during-car-qr-main\during-car-qr-main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA9F153F-5B6B-4EAA-ADFB-6EC4E4981CA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2438760-FDC5-4DA2-86A3-FBEC7E4F5A2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1351,7 +1351,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1650,6 +1650,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1658,21 +1661,7 @@
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFCCFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill>
@@ -2333,14 +2322,14 @@
       <c r="G7" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="H7" s="26" t="s">
+      <c r="H7" s="100" t="s">
         <v>48</v>
       </c>
       <c r="I7" s="23" t="s">
         <v>193</v>
       </c>
       <c r="J7" s="29">
-        <v>46168</v>
+        <v>46403</v>
       </c>
       <c r="K7" s="28">
         <v>46648</v>
@@ -2384,8 +2373,7 @@
       <c r="K8" s="28">
         <v>46645</v>
       </c>
-      <c r="L8" s="29"/>
-      <c r="M8" s="30"/>
+      <c r="M8" s="29"/>
       <c r="O8" s="15"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.4">
@@ -2411,14 +2399,14 @@
       <c r="G9" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="H9" s="26" t="s">
+      <c r="H9" s="100" t="s">
         <v>48</v>
       </c>
       <c r="I9" s="23" t="s">
         <v>193</v>
       </c>
       <c r="J9" s="29">
-        <v>46166</v>
+        <v>46403</v>
       </c>
       <c r="K9" s="28">
         <v>46531</v>
@@ -2683,19 +2671,11 @@
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C2:E13 A2:B17 C14:D14 E14:E17">
-    <cfRule type="expression" dxfId="7" priority="11">
+  <conditionalFormatting sqref="C2:E13 A2:B17 F8:K8 M8 C14:D14 E14:E17 F2:M7 F9:M17">
+    <cfRule type="expression" dxfId="5" priority="11">
       <formula>OR(#REF!="매각",#REF!="폐기",#REF!="계약종료")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="12">
-      <formula>#REF!="YES"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:M17">
-    <cfRule type="expression" dxfId="5" priority="1">
-      <formula>OR(#REF!="매각",#REF!="폐기",#REF!="계약종료")</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="4" priority="12">
       <formula>#REF!="YES"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/data/듀링 법인차량 현황 ver.2.0.xlsx
+++ b/data/듀링 법인차량 현황 ver.2.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\during-car-qr-main\during-car-qr-main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2438760-FDC5-4DA2-86A3-FBEC7E4F5A2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06BA5439-CBFC-4949-AC12-CFAA85A91D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="법인차량현황" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="238">
   <si>
     <t>차종</t>
   </si>
@@ -1351,7 +1351,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1650,9 +1650,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2322,7 +2319,7 @@
       <c r="G7" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="H7" s="100" t="s">
+      <c r="H7" s="26" t="s">
         <v>48</v>
       </c>
       <c r="I7" s="23" t="s">
@@ -2399,7 +2396,7 @@
       <c r="G9" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="H9" s="100" t="s">
+      <c r="H9" s="26" t="s">
         <v>48</v>
       </c>
       <c r="I9" s="23" t="s">
@@ -2671,7 +2668,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="C2:E13 A2:B17 F8:K8 M8 C14:D14 E14:E17 F2:M7 F9:M17">
+  <conditionalFormatting sqref="F2:M7 C2:E13 A2:B17 F8:K8 M8 F9:M17 C14:D14 E14:E17">
     <cfRule type="expression" dxfId="5" priority="11">
       <formula>OR(#REF!="매각",#REF!="폐기",#REF!="계약종료")</formula>
     </cfRule>
@@ -3000,13 +2997,27 @@
       <c r="H12" s="8"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="87"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="9"/>
+      <c r="A13" s="10">
+        <v>46182</v>
+      </c>
+      <c r="B13" s="32" t="s">
+        <v>225</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" s="87">
+        <v>77785</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G13" s="9">
+        <v>185284</v>
+      </c>
       <c r="H13" s="8"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.4">
@@ -3826,7 +3837,7 @@
       <formula>#REF!="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C11:C12">
+  <conditionalFormatting sqref="C11:C13">
     <cfRule type="expression" dxfId="1" priority="3">
       <formula>OR(#REF!="매각",#REF!="폐기",#REF!="계약종료")</formula>
     </cfRule>
@@ -3835,7 +3846,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C10 C13:C92" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C10 C14:C92" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>차량번호</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/듀링 법인차량 현황 ver.2.0.xlsx
+++ b/data/듀링 법인차량 현황 ver.2.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\during-car-qr-main\during-car-qr-main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06BA5439-CBFC-4949-AC12-CFAA85A91D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDA47EF9-E9AA-4725-BEE5-7789C80C11FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="238">
   <si>
     <t>차종</t>
   </si>
@@ -298,10 +298,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>에치에스 모터스</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>차량세차</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -319,10 +315,6 @@
   </si>
   <si>
     <t>그랜저 하이브리드</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>에치에스 모터스</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -1004,6 +996,14 @@
   </si>
   <si>
     <t>1588-5656</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>엔진오일, 타이어 4EA 교체</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>에이치에스 모터스</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2043,7 +2043,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="21" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C1" s="20" t="s">
         <v>21</v>
@@ -2052,31 +2052,31 @@
         <v>0</v>
       </c>
       <c r="E1" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F1" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="G1" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="G1" s="20" t="s">
-        <v>168</v>
-      </c>
       <c r="H1" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="I1" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="J1" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="K1" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="L1" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="M1" s="21" t="s">
         <v>182</v>
-      </c>
-      <c r="J1" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="K1" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="L1" s="21" t="s">
-        <v>183</v>
-      </c>
-      <c r="M1" s="21" t="s">
-        <v>184</v>
       </c>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
@@ -2087,10 +2087,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>40</v>
@@ -2099,16 +2099,16 @@
         <v>5</v>
       </c>
       <c r="F2" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="G2" s="22" t="s">
         <v>167</v>
-      </c>
-      <c r="G2" s="22" t="s">
-        <v>169</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>34</v>
       </c>
       <c r="I2" s="23" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J2" s="25">
         <v>46836</v>
@@ -2130,28 +2130,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D3" s="18" t="s">
         <v>39</v>
       </c>
       <c r="E3" s="23" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F3" s="19" t="s">
         <v>59</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H3" s="22" t="s">
         <v>35</v>
       </c>
       <c r="I3" s="23" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="J3" s="29">
         <v>46408</v>
@@ -2173,28 +2173,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>41</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F4" s="19" t="s">
         <v>59</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H4" s="22" t="s">
         <v>35</v>
       </c>
       <c r="I4" s="23" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="J4" s="29">
         <v>46520</v>
@@ -2216,10 +2216,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>42</v>
@@ -2231,13 +2231,13 @@
         <v>38</v>
       </c>
       <c r="G5" s="26" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H5" s="26" t="s">
         <v>34</v>
       </c>
       <c r="I5" s="23" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J5" s="29">
         <v>46474</v>
@@ -2259,10 +2259,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>42</v>
@@ -2274,13 +2274,13 @@
         <v>59</v>
       </c>
       <c r="G6" s="26" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H6" s="22" t="s">
         <v>35</v>
       </c>
       <c r="I6" s="23" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="J6" s="29">
         <v>46491</v>
@@ -2302,10 +2302,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D7" s="19" t="s">
         <v>37</v>
@@ -2317,13 +2317,13 @@
         <v>38</v>
       </c>
       <c r="G7" s="26" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H7" s="26" t="s">
         <v>48</v>
       </c>
       <c r="I7" s="23" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="J7" s="29">
         <v>46403</v>
@@ -2341,10 +2341,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>37</v>
@@ -2356,13 +2356,13 @@
         <v>38</v>
       </c>
       <c r="G8" s="26" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H8" s="26" t="s">
         <v>48</v>
       </c>
       <c r="I8" s="23" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="J8" s="29">
         <v>46403</v>
@@ -2379,10 +2379,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D9" s="19" t="s">
         <v>42</v>
@@ -2394,13 +2394,13 @@
         <v>38</v>
       </c>
       <c r="G9" s="26" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H9" s="26" t="s">
         <v>48</v>
       </c>
       <c r="I9" s="23" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="J9" s="29">
         <v>46403</v>
@@ -2418,10 +2418,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D10" s="18" t="s">
         <v>57</v>
@@ -2433,13 +2433,13 @@
         <v>38</v>
       </c>
       <c r="G10" s="26" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H10" s="26" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="I10" s="18" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J10" s="29">
         <v>46408</v>
@@ -2457,28 +2457,28 @@
         <v>10</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D11" s="35" t="s">
         <v>58</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F11" s="19" t="s">
         <v>59</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H11" s="26" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="J11" s="85">
         <v>46210</v>
@@ -2496,13 +2496,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E12" s="19" t="s">
         <v>5</v>
@@ -2511,13 +2511,13 @@
         <v>59</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H12" s="26" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I12" s="23" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="J12" s="25">
         <v>46744</v>
@@ -2539,28 +2539,28 @@
         <v>12</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F13" s="19" t="s">
         <v>38</v>
       </c>
       <c r="G13" s="26" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H13" s="26" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I13" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J13" s="29">
         <v>47847</v>
@@ -2582,28 +2582,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="23" t="s">
+        <v>224</v>
+      </c>
+      <c r="C14" s="88" t="s">
+        <v>225</v>
+      </c>
+      <c r="D14" s="88" t="s">
         <v>226</v>
       </c>
-      <c r="C14" s="88" t="s">
+      <c r="E14" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="D14" s="88" t="s">
+      <c r="F14" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="G14" s="26" t="s">
         <v>228</v>
       </c>
-      <c r="E14" s="18" t="s">
-        <v>229</v>
-      </c>
-      <c r="F14" s="19" t="s">
+      <c r="H14" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="I14" s="18" t="s">
         <v>231</v>
-      </c>
-      <c r="G14" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="H14" s="26" t="s">
-        <v>232</v>
-      </c>
-      <c r="I14" s="18" t="s">
-        <v>233</v>
       </c>
       <c r="J14" s="29">
         <v>47903</v>
@@ -2706,22 +2706,22 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="20" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C1" s="20" t="s">
         <v>21</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E1" s="20" t="s">
         <v>22</v>
       </c>
       <c r="F1" s="20" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G1" s="20" t="s">
         <v>23</v>
@@ -2735,10 +2735,10 @@
         <v>45854</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D2" s="33" t="s">
         <v>50</v>
@@ -2759,10 +2759,10 @@
         <v>45855</v>
       </c>
       <c r="B3" s="32" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D3" s="33" t="s">
         <v>55</v>
@@ -2783,10 +2783,10 @@
         <v>45883</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>43</v>
@@ -2809,10 +2809,10 @@
         <v>45888</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>54</v>
@@ -2833,10 +2833,10 @@
         <v>45890</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>45</v>
@@ -2857,10 +2857,10 @@
         <v>45915</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>60</v>
@@ -2881,10 +2881,10 @@
         <v>45975</v>
       </c>
       <c r="B8" s="32" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>62</v>
@@ -2893,7 +2893,7 @@
         <v>35734</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>63</v>
+        <v>237</v>
       </c>
       <c r="G8" s="9">
         <v>110000</v>
@@ -2905,10 +2905,10 @@
         <v>46028</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>62</v>
@@ -2917,7 +2917,7 @@
         <v>136233</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>69</v>
+        <v>237</v>
       </c>
       <c r="G9" s="9">
         <v>105000</v>
@@ -2929,10 +2929,10 @@
         <v>46043</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>60</v>
@@ -2953,10 +2953,10 @@
         <v>46050</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>60</v>
@@ -2977,19 +2977,19 @@
         <v>46105</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E12" s="87">
         <v>175843</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G12" s="9">
         <v>350000</v>
@@ -3001,10 +3001,10 @@
         <v>46182</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>60</v>
@@ -3021,16 +3021,30 @@
       <c r="H13" s="8"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="87"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="9"/>
+      <c r="A14" s="10">
+        <v>46188</v>
+      </c>
+      <c r="B14" s="32" t="s">
+        <v>221</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="E14" s="87">
+        <v>60381</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="G14" s="9">
+        <v>630000</v>
+      </c>
       <c r="H14" s="8"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="8"/>
@@ -3880,26 +3894,26 @@
   <sheetData>
     <row r="9" spans="3:35" x14ac:dyDescent="0.4">
       <c r="AA9" s="98" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="AB9" s="96" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AC9" s="59"/>
       <c r="AD9" s="37" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AE9" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="AF9" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="AG9" s="68" t="s">
+        <v>119</v>
+      </c>
+      <c r="AH9" s="37" t="s">
         <v>77</v>
-      </c>
-      <c r="AF9" s="37" t="s">
-        <v>77</v>
-      </c>
-      <c r="AG9" s="68" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH9" s="37" t="s">
-        <v>79</v>
       </c>
       <c r="AI9" s="43" t="s">
         <v>58</v>
@@ -3907,65 +3921,65 @@
     </row>
     <row r="10" spans="3:35" x14ac:dyDescent="0.4">
       <c r="C10" s="61" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D10" s="62" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="62" t="s">
+        <v>70</v>
+      </c>
+      <c r="F10" s="62" t="s">
+        <v>80</v>
+      </c>
+      <c r="G10" s="62" t="s">
         <v>71</v>
       </c>
-      <c r="E10" s="62" t="s">
+      <c r="H10" s="63" t="s">
         <v>72</v>
-      </c>
-      <c r="F10" s="62" t="s">
-        <v>82</v>
-      </c>
-      <c r="G10" s="62" t="s">
-        <v>73</v>
-      </c>
-      <c r="H10" s="63" t="s">
-        <v>74</v>
       </c>
       <c r="I10" s="79"/>
       <c r="K10" s="58" t="s">
+        <v>90</v>
+      </c>
+      <c r="L10" s="59" t="s">
         <v>92</v>
       </c>
-      <c r="L10" s="59" t="s">
-        <v>94</v>
-      </c>
       <c r="M10" s="60" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="O10" s="58" t="s">
+        <v>102</v>
+      </c>
+      <c r="P10" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="P10" s="59" t="s">
+      <c r="Q10" s="59" t="s">
+        <v>105</v>
+      </c>
+      <c r="R10" s="59" t="s">
         <v>106</v>
       </c>
-      <c r="Q10" s="59" t="s">
+      <c r="S10" s="59" t="s">
         <v>107</v>
       </c>
-      <c r="R10" s="59" t="s">
+      <c r="T10" s="59" t="s">
         <v>108</v>
       </c>
-      <c r="S10" s="59" t="s">
+      <c r="U10" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="T10" s="59" t="s">
+      <c r="V10" s="59" t="s">
         <v>110</v>
       </c>
-      <c r="U10" s="59" t="s">
+      <c r="W10" s="59" t="s">
         <v>111</v>
       </c>
-      <c r="V10" s="59" t="s">
+      <c r="X10" s="59" t="s">
         <v>112</v>
       </c>
-      <c r="W10" s="59" t="s">
+      <c r="Y10" s="60" t="s">
         <v>113</v>
-      </c>
-      <c r="X10" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="Y10" s="60" t="s">
-        <v>115</v>
       </c>
       <c r="AA10" s="99"/>
       <c r="AB10" s="97"/>
@@ -3974,13 +3988,13 @@
         <v>36</v>
       </c>
       <c r="AE10" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="AF10" t="s">
         <v>47</v>
       </c>
       <c r="AG10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AH10" t="s">
         <v>49</v>
@@ -3994,13 +4008,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E11" t="s">
         <v>36</v>
       </c>
       <c r="F11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G11" s="45">
         <v>2497</v>
@@ -4010,16 +4024,16 @@
       </c>
       <c r="I11" s="80"/>
       <c r="K11" s="95" t="s">
+        <v>91</v>
+      </c>
+      <c r="L11" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="L11" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="M11" s="56" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O11" s="47" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="P11" s="65">
         <v>0.05</v>
@@ -4055,10 +4069,10 @@
         <v>1</v>
       </c>
       <c r="AB11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AC11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AD11" s="67">
         <v>2497</v>
@@ -4084,13 +4098,13 @@
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G12" s="45">
         <v>180</v>
@@ -4101,19 +4115,19 @@
       <c r="I12" s="80"/>
       <c r="K12" s="95"/>
       <c r="L12" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="M12" s="56" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AA12" s="44">
         <v>2</v>
       </c>
       <c r="AB12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AC12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AD12">
         <v>200</v>
@@ -4131,13 +4145,13 @@
         <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E13" t="s">
         <v>47</v>
       </c>
       <c r="F13" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G13" s="45">
         <v>180</v>
@@ -4148,19 +4162,19 @@
       <c r="I13" s="80"/>
       <c r="K13" s="95"/>
       <c r="L13" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M13" s="56" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AA13" s="44">
         <v>3</v>
       </c>
       <c r="AB13" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="AC13" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="AD13" s="45">
         <f>AD11*AD12</f>
@@ -4189,13 +4203,13 @@
         <v>4</v>
       </c>
       <c r="D14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E14" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G14" s="45">
         <v>1999</v>
@@ -4206,19 +4220,19 @@
       <c r="I14" s="80"/>
       <c r="K14" s="91"/>
       <c r="L14" s="41" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="M14" s="57" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AA14" s="44">
         <v>4</v>
       </c>
       <c r="AB14" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="AC14" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AD14" s="69">
         <v>1</v>
@@ -4244,13 +4258,13 @@
         <v>5</v>
       </c>
       <c r="D15" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E15" t="s">
         <v>49</v>
       </c>
       <c r="F15" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G15" s="45">
         <v>1591</v>
@@ -4263,10 +4277,10 @@
         <v>5</v>
       </c>
       <c r="AB15" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AC15" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AD15" s="45">
         <v>499400</v>
@@ -4300,7 +4314,7 @@
         <v>56</v>
       </c>
       <c r="F16" s="48" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G16" s="49">
         <v>111</v>
@@ -4313,10 +4327,10 @@
         <v>8</v>
       </c>
       <c r="AB16" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="AC16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AD16" s="69">
         <v>0.3</v>
@@ -4342,10 +4356,10 @@
         <v>9</v>
       </c>
       <c r="AB17" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AC17" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AD17" s="71">
         <f>AD15*0.3</f>
@@ -4374,10 +4388,10 @@
         <v>10</v>
       </c>
       <c r="AB18" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AC18" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="AD18" s="74">
         <v>29710</v>
@@ -4403,10 +4417,10 @@
         <v>11</v>
       </c>
       <c r="AB19" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AC19" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AD19" s="77">
         <f>AD15+AD17-AD18</f>
@@ -4435,22 +4449,22 @@
     </row>
     <row r="20" spans="3:35" x14ac:dyDescent="0.4">
       <c r="C20" s="61" t="s">
+        <v>85</v>
+      </c>
+      <c r="D20" s="62" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" s="62" t="s">
+        <v>70</v>
+      </c>
+      <c r="F20" s="62" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="62" t="s">
-        <v>71</v>
-      </c>
-      <c r="E20" s="62" t="s">
-        <v>72</v>
-      </c>
-      <c r="F20" s="62" t="s">
-        <v>89</v>
-      </c>
       <c r="G20" s="62" t="s">
+        <v>86</v>
+      </c>
+      <c r="H20" s="63" t="s">
         <v>88</v>
-      </c>
-      <c r="H20" s="63" t="s">
-        <v>90</v>
       </c>
       <c r="I20" s="79"/>
       <c r="AA20" s="37"/>
@@ -4468,7 +4482,7 @@
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E21" t="s">
         <v>36</v>
@@ -4492,10 +4506,10 @@
         <v>2</v>
       </c>
       <c r="D22" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E22" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F22" s="45">
         <v>95420</v>
@@ -4519,7 +4533,7 @@
         <v>3</v>
       </c>
       <c r="D23" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E23" t="s">
         <v>47</v>
@@ -4542,10 +4556,10 @@
         <v>4</v>
       </c>
       <c r="D24" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E24" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F24" s="45">
         <v>305200</v>
@@ -4565,7 +4579,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E25" t="s">
         <v>49</v>
@@ -4606,7 +4620,7 @@
     </row>
     <row r="27" spans="3:35" x14ac:dyDescent="0.4">
       <c r="C27" s="93" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D27" s="94"/>
       <c r="E27" s="94"/>
@@ -4626,13 +4640,13 @@
     </row>
     <row r="30" spans="3:35" x14ac:dyDescent="0.4">
       <c r="C30" s="58" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D30" s="59" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E30" s="59" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F30" s="59">
         <v>2024</v>
@@ -4644,13 +4658,13 @@
         <v>2026</v>
       </c>
       <c r="I30" s="59" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="J30" s="59" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K30" s="63" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="3:35" x14ac:dyDescent="0.4">
@@ -4658,7 +4672,7 @@
         <v>1</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>36</v>
@@ -4672,13 +4686,13 @@
         <v>619510</v>
       </c>
       <c r="I31" s="84" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J31" s="83" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="K31" s="51" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="32" spans="3:35" x14ac:dyDescent="0.4">
@@ -4686,10 +4700,10 @@
         <v>2</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F32" s="40"/>
       <c r="G32" s="40">
@@ -4699,13 +4713,13 @@
         <v>124040</v>
       </c>
       <c r="I32" s="40" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="K32" s="51" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="33" spans="3:11" x14ac:dyDescent="0.4">
@@ -4713,7 +4727,7 @@
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>47</v>
@@ -4726,13 +4740,13 @@
         <v>124040</v>
       </c>
       <c r="I33" s="40" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K33" s="51" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="34" spans="3:11" x14ac:dyDescent="0.4">
@@ -4740,10 +4754,10 @@
         <v>4</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F34" s="40">
         <v>34680</v>
@@ -4755,10 +4769,10 @@
         <v>396760</v>
       </c>
       <c r="I34" s="40" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K34" s="51"/>
     </row>
@@ -4767,7 +4781,7 @@
         <v>5</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>49</v>
@@ -4782,10 +4796,10 @@
         <v>172690</v>
       </c>
       <c r="I35" s="40" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="K35" s="51"/>
     </row>
@@ -4818,7 +4832,7 @@
     </row>
     <row r="37" spans="3:11" x14ac:dyDescent="0.4">
       <c r="C37" s="91" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D37" s="92"/>
       <c r="E37" s="92"/>
@@ -4835,10 +4849,10 @@
         <v>1837710</v>
       </c>
       <c r="I37" s="82" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J37" s="82" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="K37" s="52"/>
     </row>
@@ -4974,7 +4988,7 @@
         <v>10</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J8" s="4"/>
     </row>
